--- a/data/england/p6_deployment/data_preparation/clean_data/df_match_player_cleaned.xlsx
+++ b/data/england/p6_deployment/data_preparation/clean_data/df_match_player_cleaned.xlsx
@@ -425,15 +425,41 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:A47"/>
+  <dimension ref="A1:E57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_1</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_1</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_1</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_1</t>
+        </is>
+      </c>
+    </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
           <t>Kl1AOZN9</t>
         </is>
       </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -441,6 +467,10 @@
           <t>t4kJMDhM</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -448,6 +478,10 @@
           <t>CntkHiGq</t>
         </is>
       </c>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -455,6 +489,10 @@
           <t>hdlcFVpd</t>
         </is>
       </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -462,6 +500,10 @@
           <t>pjyqwZx3</t>
         </is>
       </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -469,6 +511,10 @@
           <t>tIUiyD7F</t>
         </is>
       </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -476,6 +522,10 @@
           <t>nHdPI4il</t>
         </is>
       </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
@@ -483,6 +533,10 @@
           <t>8WpYGrM0</t>
         </is>
       </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -490,6 +544,10 @@
           <t>fmqtFMjD</t>
         </is>
       </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
@@ -497,258 +555,532 @@
           <t>AeRSxQrK</t>
         </is>
       </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>tYjCfe2E</t>
-        </is>
-      </c>
+          <t>8j9FTL56</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>OMDVg8x9</t>
-        </is>
-      </c>
+          <t>U5cORazJ</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>jXcAnQUr</t>
-        </is>
-      </c>
+          <t>dCkAk3SP</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>fRe0c20b</t>
-        </is>
-      </c>
+          <t>lAUlrLKa</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>CnnJp4ae</t>
-        </is>
-      </c>
+          <t>fNaktakC</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>bw1zAKS6</t>
-        </is>
-      </c>
+          <t>2m3cvwKO</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>GINCsvmn</t>
-        </is>
-      </c>
+          <t>2g67Vsyf</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>x6klsVh3</t>
-        </is>
-      </c>
+          <t>6RCbX36s</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>b3pRrrU7</t>
-        </is>
-      </c>
+          <t>61T7bt5t</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>WfkfPdXH</t>
-        </is>
-      </c>
+          <t>GdWtpsjm</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>SMr3Nz2U</t>
+          <t>tYjCfe2E</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>xOoNh0S7</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>kabore issa</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>OdyMQkkR</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>malacia tyrell</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>xYBLuIHb</t>
-        </is>
-      </c>
+          <t>OMDVg8x9</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr"/>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6os5wmhS</t>
-        </is>
-      </c>
+          <t>jXcAnQUr</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr"/>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>Kl7vhn7L</t>
-        </is>
-      </c>
+          <t>fRe0c20b</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr"/>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>nw6fJO5K</t>
-        </is>
-      </c>
+          <t>CnnJp4ae</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr"/>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>bHPacsq1</t>
-        </is>
-      </c>
+          <t>bw1zAKS6</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr"/>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>MwmHgKaN</t>
-        </is>
-      </c>
+          <t>GINCsvmn</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr"/>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>lQl9etVA</t>
-        </is>
-      </c>
+          <t>x6klsVh3</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr"/>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>KWD8eLDD</t>
-        </is>
-      </c>
+          <t>b3pRrrU7</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr"/>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>xUXzYQFk</t>
-        </is>
-      </c>
+          <t>WfkfPdXH</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr"/>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>CCV9JR0d</t>
-        </is>
-      </c>
+          <t>SMr3Nz2U</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr"/>
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>bsinRI25</t>
-        </is>
-      </c>
+          <t>xYBLuIHb</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr"/>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>GbaVU03t</t>
-        </is>
-      </c>
+          <t>6os5wmhS</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr"/>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>tOTmlbNp</t>
-        </is>
-      </c>
+          <t>Kl7vhn7L</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr"/>
+      <c r="C35" t="inlineStr"/>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>nPQL4PjR</t>
-        </is>
-      </c>
+          <t>nw6fJO5K</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr"/>
+      <c r="C36" t="inlineStr"/>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>pWhdu9NF</t>
-        </is>
-      </c>
+          <t>bHPacsq1</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr"/>
+      <c r="C37" t="inlineStr"/>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>6NnRD2Ts</t>
-        </is>
-      </c>
+          <t>MwmHgKaN</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr"/>
+      <c r="C38" t="inlineStr"/>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>2FcwTvYh</t>
-        </is>
-      </c>
+          <t>lQl9etVA</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr"/>
+      <c r="C39" t="inlineStr"/>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>EBSD6oME</t>
-        </is>
-      </c>
+          <t>KWD8eLDD</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr"/>
+      <c r="C40" t="inlineStr"/>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>WSQqW4p2</t>
-        </is>
-      </c>
+          <t>xUXzYQFk</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr"/>
+      <c r="C41" t="inlineStr"/>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>vaX1LmWq</t>
-        </is>
-      </c>
+          <t>CCV9JR0d</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr"/>
+      <c r="C42" t="inlineStr"/>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>n1hhaOVo</t>
-        </is>
-      </c>
+          <t>bsinRI25</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr"/>
+      <c r="C43" t="inlineStr"/>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>vyoZBtbf</t>
-        </is>
-      </c>
+          <t>GbaVU03t</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr"/>
+      <c r="C44" t="inlineStr"/>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>634r8bcJ</t>
-        </is>
-      </c>
+          <t>tOTmlbNp</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr"/>
+      <c r="C45" t="inlineStr"/>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>pbFTwdnB</t>
-        </is>
-      </c>
+          <t>nPQL4PjR</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr"/>
+      <c r="C46" t="inlineStr"/>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
+          <t>pWhdu9NF</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr"/>
+      <c r="C47" t="inlineStr"/>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="inlineStr">
+        <is>
+          <t>6NnRD2Ts</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr"/>
+      <c r="C48" t="inlineStr"/>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="1" t="inlineStr">
+        <is>
+          <t>2FcwTvYh</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr"/>
+      <c r="C49" t="inlineStr"/>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="1" t="inlineStr">
+        <is>
+          <t>EBSD6oME</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr"/>
+      <c r="C50" t="inlineStr"/>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="inlineStr">
+        <is>
+          <t>WSQqW4p2</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr"/>
+      <c r="C51" t="inlineStr"/>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="1" t="inlineStr">
+        <is>
+          <t>vaX1LmWq</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr"/>
+      <c r="C52" t="inlineStr"/>
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="1" t="inlineStr">
+        <is>
+          <t>n1hhaOVo</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr"/>
+      <c r="C53" t="inlineStr"/>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="1" t="inlineStr">
+        <is>
+          <t>vyoZBtbf</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr"/>
+      <c r="C54" t="inlineStr"/>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="1" t="inlineStr">
+        <is>
+          <t>634r8bcJ</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr"/>
+      <c r="C55" t="inlineStr"/>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="1" t="inlineStr">
+        <is>
+          <t>pbFTwdnB</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr"/>
+      <c r="C56" t="inlineStr"/>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="1" t="inlineStr">
+        <is>
           <t>697ha3El</t>
         </is>
       </c>
+      <c r="B57" t="inlineStr"/>
+      <c r="C57" t="inlineStr"/>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/england/p6_deployment/data_preparation/clean_data/df_match_player_cleaned.xlsx
+++ b/data/england/p6_deployment/data_preparation/clean_data/df_match_player_cleaned.xlsx
@@ -425,28 +425,48 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E57"/>
+  <dimension ref="A1:I47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>id_player_miss_home_1</t>
+          <t>id_player_miss_away_1</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>player_name_miss_home_1</t>
+          <t>player_name_miss_away_1</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>id_player_miss_away_1</t>
+          <t>id_player_miss_away_2</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>player_name_miss_away_1</t>
+          <t>player_name_miss_away_2</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_3</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_3</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_4</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_4</t>
         </is>
       </c>
     </row>
@@ -460,6 +480,10 @@
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -471,6 +495,10 @@
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -482,6 +510,10 @@
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -493,6 +525,10 @@
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -504,6 +540,10 @@
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -515,6 +555,10 @@
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -526,6 +570,10 @@
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
@@ -537,6 +585,10 @@
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -548,6 +600,10 @@
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
@@ -559,528 +615,582 @@
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>8j9FTL56</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
+          <t>tYjCfe2E</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>tKOLurpo</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>fish william</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>0lk9Mt7D</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>hojlund rasmus</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>OdyMQkkR</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>malacia tyrell</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>hSGFyXra</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>yoro leny</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>U5cORazJ</t>
+          <t>OMDVg8x9</t>
         </is>
       </c>
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>dCkAk3SP</t>
+          <t>jXcAnQUr</t>
         </is>
       </c>
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>lAUlrLKa</t>
+          <t>fRe0c20b</t>
         </is>
       </c>
       <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>fNaktakC</t>
+          <t>CnnJp4ae</t>
         </is>
       </c>
       <c r="B16" t="inlineStr"/>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>2m3cvwKO</t>
+          <t>bw1zAKS6</t>
         </is>
       </c>
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>2g67Vsyf</t>
+          <t>GINCsvmn</t>
         </is>
       </c>
       <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6RCbX36s</t>
+          <t>x6klsVh3</t>
         </is>
       </c>
       <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>61T7bt5t</t>
+          <t>b3pRrrU7</t>
         </is>
       </c>
       <c r="B20" t="inlineStr"/>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>GdWtpsjm</t>
+          <t>WfkfPdXH</t>
         </is>
       </c>
       <c r="B21" t="inlineStr"/>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>tYjCfe2E</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>xOoNh0S7</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>kabore issa</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>OdyMQkkR</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>malacia tyrell</t>
-        </is>
-      </c>
+          <t>SMr3Nz2U</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>OMDVg8x9</t>
+          <t>xYBLuIHb</t>
         </is>
       </c>
       <c r="B23" t="inlineStr"/>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>jXcAnQUr</t>
+          <t>6os5wmhS</t>
         </is>
       </c>
       <c r="B24" t="inlineStr"/>
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>fRe0c20b</t>
+          <t>Kl7vhn7L</t>
         </is>
       </c>
       <c r="B25" t="inlineStr"/>
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>CnnJp4ae</t>
+          <t>nw6fJO5K</t>
         </is>
       </c>
       <c r="B26" t="inlineStr"/>
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>bw1zAKS6</t>
+          <t>bHPacsq1</t>
         </is>
       </c>
       <c r="B27" t="inlineStr"/>
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>GINCsvmn</t>
+          <t>MwmHgKaN</t>
         </is>
       </c>
       <c r="B28" t="inlineStr"/>
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>x6klsVh3</t>
+          <t>lQl9etVA</t>
         </is>
       </c>
       <c r="B29" t="inlineStr"/>
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>b3pRrrU7</t>
+          <t>KWD8eLDD</t>
         </is>
       </c>
       <c r="B30" t="inlineStr"/>
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>WfkfPdXH</t>
+          <t>xUXzYQFk</t>
         </is>
       </c>
       <c r="B31" t="inlineStr"/>
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>SMr3Nz2U</t>
+          <t>CCV9JR0d</t>
         </is>
       </c>
       <c r="B32" t="inlineStr"/>
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>xYBLuIHb</t>
+          <t>bsinRI25</t>
         </is>
       </c>
       <c r="B33" t="inlineStr"/>
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>6os5wmhS</t>
+          <t>GbaVU03t</t>
         </is>
       </c>
       <c r="B34" t="inlineStr"/>
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>Kl7vhn7L</t>
+          <t>tOTmlbNp</t>
         </is>
       </c>
       <c r="B35" t="inlineStr"/>
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>nw6fJO5K</t>
+          <t>nPQL4PjR</t>
         </is>
       </c>
       <c r="B36" t="inlineStr"/>
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>bHPacsq1</t>
+          <t>pWhdu9NF</t>
         </is>
       </c>
       <c r="B37" t="inlineStr"/>
       <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>MwmHgKaN</t>
+          <t>6NnRD2Ts</t>
         </is>
       </c>
       <c r="B38" t="inlineStr"/>
       <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>lQl9etVA</t>
+          <t>2FcwTvYh</t>
         </is>
       </c>
       <c r="B39" t="inlineStr"/>
       <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr"/>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>KWD8eLDD</t>
+          <t>EBSD6oME</t>
         </is>
       </c>
       <c r="B40" t="inlineStr"/>
       <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr"/>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>xUXzYQFk</t>
+          <t>WSQqW4p2</t>
         </is>
       </c>
       <c r="B41" t="inlineStr"/>
       <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>CCV9JR0d</t>
+          <t>vaX1LmWq</t>
         </is>
       </c>
       <c r="B42" t="inlineStr"/>
       <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr"/>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>bsinRI25</t>
+          <t>n1hhaOVo</t>
         </is>
       </c>
       <c r="B43" t="inlineStr"/>
       <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr"/>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>GbaVU03t</t>
+          <t>vyoZBtbf</t>
         </is>
       </c>
       <c r="B44" t="inlineStr"/>
       <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr"/>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>tOTmlbNp</t>
+          <t>634r8bcJ</t>
         </is>
       </c>
       <c r="B45" t="inlineStr"/>
       <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr"/>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>nPQL4PjR</t>
+          <t>pbFTwdnB</t>
         </is>
       </c>
       <c r="B46" t="inlineStr"/>
       <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr"/>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>pWhdu9NF</t>
+          <t>697ha3El</t>
         </is>
       </c>
       <c r="B47" t="inlineStr"/>
       <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="1" t="inlineStr">
-        <is>
-          <t>6NnRD2Ts</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr"/>
-      <c r="C48" t="inlineStr"/>
-      <c r="D48" t="inlineStr"/>
-      <c r="E48" t="inlineStr"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="1" t="inlineStr">
-        <is>
-          <t>2FcwTvYh</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr"/>
-      <c r="C49" t="inlineStr"/>
-      <c r="D49" t="inlineStr"/>
-      <c r="E49" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="1" t="inlineStr">
-        <is>
-          <t>EBSD6oME</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr"/>
-      <c r="C50" t="inlineStr"/>
-      <c r="D50" t="inlineStr"/>
-      <c r="E50" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="1" t="inlineStr">
-        <is>
-          <t>WSQqW4p2</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr"/>
-      <c r="C51" t="inlineStr"/>
-      <c r="D51" t="inlineStr"/>
-      <c r="E51" t="inlineStr"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="1" t="inlineStr">
-        <is>
-          <t>vaX1LmWq</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr"/>
-      <c r="C52" t="inlineStr"/>
-      <c r="D52" t="inlineStr"/>
-      <c r="E52" t="inlineStr"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="1" t="inlineStr">
-        <is>
-          <t>n1hhaOVo</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr"/>
-      <c r="C53" t="inlineStr"/>
-      <c r="D53" t="inlineStr"/>
-      <c r="E53" t="inlineStr"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="1" t="inlineStr">
-        <is>
-          <t>vyoZBtbf</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr"/>
-      <c r="C54" t="inlineStr"/>
-      <c r="D54" t="inlineStr"/>
-      <c r="E54" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="1" t="inlineStr">
-        <is>
-          <t>634r8bcJ</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr"/>
-      <c r="C55" t="inlineStr"/>
-      <c r="D55" t="inlineStr"/>
-      <c r="E55" t="inlineStr"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="1" t="inlineStr">
-        <is>
-          <t>pbFTwdnB</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr"/>
-      <c r="C56" t="inlineStr"/>
-      <c r="D56" t="inlineStr"/>
-      <c r="E56" t="inlineStr"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="1" t="inlineStr">
-        <is>
-          <t>697ha3El</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr"/>
-      <c r="C57" t="inlineStr"/>
-      <c r="D57" t="inlineStr"/>
-      <c r="E57" t="inlineStr"/>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/england/p6_deployment/data_preparation/clean_data/df_match_player_cleaned.xlsx
+++ b/data/england/p6_deployment/data_preparation/clean_data/df_match_player_cleaned.xlsx
@@ -425,41 +425,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E57"/>
+  <dimension ref="A2:A56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1">
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_home_1</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_home_1</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_away_1</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_away_1</t>
-        </is>
-      </c>
-    </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
           <t>Kl1AOZN9</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -467,10 +441,6 @@
           <t>t4kJMDhM</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -478,10 +448,6 @@
           <t>CntkHiGq</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -489,10 +455,6 @@
           <t>hdlcFVpd</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -500,10 +462,6 @@
           <t>pjyqwZx3</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -511,10 +469,6 @@
           <t>tIUiyD7F</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -522,10 +476,6 @@
           <t>nHdPI4il</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
@@ -533,10 +483,6 @@
           <t>8WpYGrM0</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -544,10 +490,6 @@
           <t>fmqtFMjD</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
@@ -555,10 +497,6 @@
           <t>AeRSxQrK</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
@@ -566,10 +504,6 @@
           <t>8j9FTL56</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
@@ -577,10 +511,6 @@
           <t>U5cORazJ</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
@@ -588,10 +518,6 @@
           <t>dCkAk3SP</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
@@ -599,10 +525,6 @@
           <t>lAUlrLKa</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
@@ -610,10 +532,6 @@
           <t>fNaktakC</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
@@ -621,10 +539,6 @@
           <t>2m3cvwKO</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr"/>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
@@ -632,10 +546,6 @@
           <t>2g67Vsyf</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr"/>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
@@ -643,10 +553,6 @@
           <t>6RCbX36s</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr"/>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
@@ -654,10 +560,6 @@
           <t>61T7bt5t</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr"/>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
@@ -665,422 +567,251 @@
           <t>GdWtpsjm</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr"/>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>tYjCfe2E</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>xOoNh0S7</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>kabore issa</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>OdyMQkkR</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>malacia tyrell</t>
+          <t>OMDVg8x9</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>OMDVg8x9</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr"/>
-      <c r="C23" t="inlineStr"/>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr"/>
+          <t>jXcAnQUr</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>jXcAnQUr</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr"/>
-      <c r="C24" t="inlineStr"/>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr"/>
+          <t>fRe0c20b</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>fRe0c20b</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr"/>
-      <c r="C25" t="inlineStr"/>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr"/>
+          <t>CnnJp4ae</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>CnnJp4ae</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr"/>
-      <c r="C26" t="inlineStr"/>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr"/>
+          <t>bw1zAKS6</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>bw1zAKS6</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr"/>
-      <c r="C27" t="inlineStr"/>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr"/>
+          <t>GINCsvmn</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>GINCsvmn</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr"/>
-      <c r="C28" t="inlineStr"/>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr"/>
+          <t>x6klsVh3</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>x6klsVh3</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr"/>
-      <c r="C29" t="inlineStr"/>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr"/>
+          <t>b3pRrrU7</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>b3pRrrU7</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr"/>
-      <c r="C30" t="inlineStr"/>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr"/>
+          <t>WfkfPdXH</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>WfkfPdXH</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr"/>
-      <c r="C31" t="inlineStr"/>
-      <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr"/>
+          <t>SMr3Nz2U</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>SMr3Nz2U</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr"/>
-      <c r="C32" t="inlineStr"/>
-      <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr"/>
+          <t>xYBLuIHb</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>xYBLuIHb</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr"/>
-      <c r="C33" t="inlineStr"/>
-      <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr"/>
+          <t>6os5wmhS</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>6os5wmhS</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr"/>
-      <c r="C34" t="inlineStr"/>
-      <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr"/>
+          <t>Kl7vhn7L</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>Kl7vhn7L</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr"/>
-      <c r="C35" t="inlineStr"/>
-      <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr"/>
+          <t>nw6fJO5K</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>nw6fJO5K</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr"/>
-      <c r="C36" t="inlineStr"/>
-      <c r="D36" t="inlineStr"/>
-      <c r="E36" t="inlineStr"/>
+          <t>bHPacsq1</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>bHPacsq1</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr"/>
-      <c r="C37" t="inlineStr"/>
-      <c r="D37" t="inlineStr"/>
-      <c r="E37" t="inlineStr"/>
+          <t>MwmHgKaN</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>MwmHgKaN</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr"/>
-      <c r="C38" t="inlineStr"/>
-      <c r="D38" t="inlineStr"/>
-      <c r="E38" t="inlineStr"/>
+          <t>lQl9etVA</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>lQl9etVA</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr"/>
-      <c r="C39" t="inlineStr"/>
-      <c r="D39" t="inlineStr"/>
-      <c r="E39" t="inlineStr"/>
+          <t>KWD8eLDD</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>KWD8eLDD</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr"/>
-      <c r="C40" t="inlineStr"/>
-      <c r="D40" t="inlineStr"/>
-      <c r="E40" t="inlineStr"/>
+          <t>xUXzYQFk</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>xUXzYQFk</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr"/>
-      <c r="C41" t="inlineStr"/>
-      <c r="D41" t="inlineStr"/>
-      <c r="E41" t="inlineStr"/>
+          <t>CCV9JR0d</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>CCV9JR0d</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr"/>
-      <c r="C42" t="inlineStr"/>
-      <c r="D42" t="inlineStr"/>
-      <c r="E42" t="inlineStr"/>
+          <t>bsinRI25</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>bsinRI25</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr"/>
-      <c r="C43" t="inlineStr"/>
-      <c r="D43" t="inlineStr"/>
-      <c r="E43" t="inlineStr"/>
+          <t>GbaVU03t</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>GbaVU03t</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr"/>
-      <c r="C44" t="inlineStr"/>
-      <c r="D44" t="inlineStr"/>
-      <c r="E44" t="inlineStr"/>
+          <t>tOTmlbNp</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>tOTmlbNp</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr"/>
-      <c r="C45" t="inlineStr"/>
-      <c r="D45" t="inlineStr"/>
-      <c r="E45" t="inlineStr"/>
+          <t>nPQL4PjR</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>nPQL4PjR</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr"/>
-      <c r="C46" t="inlineStr"/>
-      <c r="D46" t="inlineStr"/>
-      <c r="E46" t="inlineStr"/>
+          <t>pWhdu9NF</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>pWhdu9NF</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr"/>
-      <c r="C47" t="inlineStr"/>
-      <c r="D47" t="inlineStr"/>
-      <c r="E47" t="inlineStr"/>
+          <t>6NnRD2Ts</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>6NnRD2Ts</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr"/>
-      <c r="C48" t="inlineStr"/>
-      <c r="D48" t="inlineStr"/>
-      <c r="E48" t="inlineStr"/>
+          <t>2FcwTvYh</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>2FcwTvYh</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr"/>
-      <c r="C49" t="inlineStr"/>
-      <c r="D49" t="inlineStr"/>
-      <c r="E49" t="inlineStr"/>
+          <t>EBSD6oME</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>EBSD6oME</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr"/>
-      <c r="C50" t="inlineStr"/>
-      <c r="D50" t="inlineStr"/>
-      <c r="E50" t="inlineStr"/>
+          <t>WSQqW4p2</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>WSQqW4p2</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr"/>
-      <c r="C51" t="inlineStr"/>
-      <c r="D51" t="inlineStr"/>
-      <c r="E51" t="inlineStr"/>
+          <t>vaX1LmWq</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>vaX1LmWq</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr"/>
-      <c r="C52" t="inlineStr"/>
-      <c r="D52" t="inlineStr"/>
-      <c r="E52" t="inlineStr"/>
+          <t>n1hhaOVo</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>n1hhaOVo</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr"/>
-      <c r="C53" t="inlineStr"/>
-      <c r="D53" t="inlineStr"/>
-      <c r="E53" t="inlineStr"/>
+          <t>vyoZBtbf</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>vyoZBtbf</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr"/>
-      <c r="C54" t="inlineStr"/>
-      <c r="D54" t="inlineStr"/>
-      <c r="E54" t="inlineStr"/>
+          <t>634r8bcJ</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>634r8bcJ</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr"/>
-      <c r="C55" t="inlineStr"/>
-      <c r="D55" t="inlineStr"/>
-      <c r="E55" t="inlineStr"/>
+          <t>pbFTwdnB</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>pbFTwdnB</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr"/>
-      <c r="C56" t="inlineStr"/>
-      <c r="D56" t="inlineStr"/>
-      <c r="E56" t="inlineStr"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="1" t="inlineStr">
-        <is>
           <t>697ha3El</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr"/>
-      <c r="C57" t="inlineStr"/>
-      <c r="D57" t="inlineStr"/>
-      <c r="E57" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/england/p6_deployment/data_preparation/clean_data/df_match_player_cleaned.xlsx
+++ b/data/england/p6_deployment/data_preparation/clean_data/df_match_player_cleaned.xlsx
@@ -425,393 +425,882 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:A56"/>
+  <dimension ref="A1:K47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_1</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_1</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_2</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_2</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_3</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_3</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_1</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_1</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_2</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_2</t>
+        </is>
+      </c>
+    </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Kl1AOZN9</t>
+          <t>AeRSxQrK</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>8YT7Leas</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>coady conor</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>0MQtpIlG</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>daka patson</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>fP3OohgD</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>vardy jamie</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>CSdILBh7</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>bissouma yves</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>SWLt6Trt</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>forster fraser</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>t4kJMDhM</t>
-        </is>
-      </c>
+          <t>8j9FTL56</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>CntkHiGq</t>
-        </is>
-      </c>
+          <t>U5cORazJ</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hdlcFVpd</t>
-        </is>
-      </c>
+          <t>dCkAk3SP</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>pjyqwZx3</t>
-        </is>
-      </c>
+          <t>lAUlrLKa</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>tIUiyD7F</t>
-        </is>
-      </c>
+          <t>fNaktakC</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>nHdPI4il</t>
-        </is>
-      </c>
+          <t>2m3cvwKO</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>8WpYGrM0</t>
-        </is>
-      </c>
+          <t>2g67Vsyf</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>fmqtFMjD</t>
-        </is>
-      </c>
+          <t>6RCbX36s</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>AeRSxQrK</t>
-        </is>
-      </c>
+          <t>61T7bt5t</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>8j9FTL56</t>
-        </is>
-      </c>
+          <t>GdWtpsjm</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>U5cORazJ</t>
-        </is>
-      </c>
+          <t>ERWFdKZh</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>dCkAk3SP</t>
-        </is>
-      </c>
+          <t>8QPOfb45</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>lAUlrLKa</t>
-        </is>
-      </c>
+          <t>x6HuiG3U</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>fNaktakC</t>
-        </is>
-      </c>
+          <t>SUdkBJln</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>2m3cvwKO</t>
-        </is>
-      </c>
+          <t>lpob9cJb</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>2g67Vsyf</t>
-        </is>
-      </c>
+          <t>2Fanm72d</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6RCbX36s</t>
-        </is>
-      </c>
+          <t>INsZAAf3</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>61T7bt5t</t>
-        </is>
-      </c>
+          <t>tvOWhxZH</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>GdWtpsjm</t>
-        </is>
-      </c>
+          <t>U11vkTXq</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>OMDVg8x9</t>
-        </is>
-      </c>
+          <t>z1q67ylB</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>jXcAnQUr</t>
-        </is>
-      </c>
+          <t>U32wGjPp</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr"/>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>fRe0c20b</t>
-        </is>
-      </c>
+          <t>dUjtW2Fr</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr"/>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>CnnJp4ae</t>
-        </is>
-      </c>
+          <t>MFnpCm7C</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr"/>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>bw1zAKS6</t>
-        </is>
-      </c>
+          <t>Wn71woN8</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr"/>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>GINCsvmn</t>
-        </is>
-      </c>
+          <t>UsklUtpe</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr"/>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>x6klsVh3</t>
-        </is>
-      </c>
+          <t>hGzqjO6E</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr"/>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>b3pRrrU7</t>
-        </is>
-      </c>
+          <t>OrHrRGXo</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr"/>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>WfkfPdXH</t>
-        </is>
-      </c>
+          <t>Sh9BS8ig</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr"/>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>SMr3Nz2U</t>
-        </is>
-      </c>
+          <t>EkqxE9x0</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr"/>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>xYBLuIHb</t>
-        </is>
-      </c>
+          <t>dAfPwfHi</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr"/>
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>6os5wmhS</t>
-        </is>
-      </c>
+          <t>pWQ6LC1N</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr"/>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>Kl7vhn7L</t>
-        </is>
-      </c>
+          <t>jiUEFsV1</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr"/>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>nw6fJO5K</t>
-        </is>
-      </c>
+          <t>dY0SOQjI</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr"/>
+      <c r="C35" t="inlineStr"/>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>bHPacsq1</t>
-        </is>
-      </c>
+          <t>hO8aNYWA</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr"/>
+      <c r="C36" t="inlineStr"/>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>MwmHgKaN</t>
-        </is>
-      </c>
+          <t>rRQ6H30k</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr"/>
+      <c r="C37" t="inlineStr"/>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>lQl9etVA</t>
-        </is>
-      </c>
+          <t>vDA9yPiL</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr"/>
+      <c r="C38" t="inlineStr"/>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>KWD8eLDD</t>
-        </is>
-      </c>
+          <t>hzeTFV7m</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr"/>
+      <c r="C39" t="inlineStr"/>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>xUXzYQFk</t>
-        </is>
-      </c>
+          <t>Q9rcSKE7</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr"/>
+      <c r="C40" t="inlineStr"/>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr"/>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>CCV9JR0d</t>
-        </is>
-      </c>
+          <t>WQF2UUMt</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr"/>
+      <c r="C41" t="inlineStr"/>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>bsinRI25</t>
-        </is>
-      </c>
+          <t>zJCJQnM5</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr"/>
+      <c r="C42" t="inlineStr"/>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>GbaVU03t</t>
-        </is>
-      </c>
+          <t>QkntzCGG</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr"/>
+      <c r="C43" t="inlineStr"/>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>tOTmlbNp</t>
-        </is>
-      </c>
+          <t>rkazN4LU</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr"/>
+      <c r="C44" t="inlineStr"/>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr"/>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>nPQL4PjR</t>
-        </is>
-      </c>
+          <t>ddFjPf2b</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr"/>
+      <c r="C45" t="inlineStr"/>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr"/>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>pWhdu9NF</t>
-        </is>
-      </c>
+          <t>hxlYyYo4</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr"/>
+      <c r="C46" t="inlineStr"/>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr"/>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>6NnRD2Ts</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="1" t="inlineStr">
-        <is>
-          <t>2FcwTvYh</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="1" t="inlineStr">
-        <is>
-          <t>EBSD6oME</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="1" t="inlineStr">
-        <is>
-          <t>WSQqW4p2</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="1" t="inlineStr">
-        <is>
-          <t>vaX1LmWq</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="1" t="inlineStr">
-        <is>
-          <t>n1hhaOVo</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="1" t="inlineStr">
-        <is>
-          <t>vyoZBtbf</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="1" t="inlineStr">
-        <is>
-          <t>634r8bcJ</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="1" t="inlineStr">
-        <is>
-          <t>pbFTwdnB</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="1" t="inlineStr">
-        <is>
-          <t>697ha3El</t>
-        </is>
-      </c>
+          <t>GEugARyP</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr"/>
+      <c r="C47" t="inlineStr"/>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr"/>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/england/p6_deployment/data_preparation/clean_data/df_match_player_cleaned.xlsx
+++ b/data/england/p6_deployment/data_preparation/clean_data/df_match_player_cleaned.xlsx
@@ -425,391 +425,321 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:A56"/>
+  <dimension ref="A2:A46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Kl1AOZN9</t>
+          <t>8j9FTL56</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>t4kJMDhM</t>
+          <t>U5cORazJ</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>CntkHiGq</t>
+          <t>dCkAk3SP</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hdlcFVpd</t>
+          <t>lAUlrLKa</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>pjyqwZx3</t>
+          <t>fNaktakC</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>tIUiyD7F</t>
+          <t>2m3cvwKO</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>nHdPI4il</t>
+          <t>2g67Vsyf</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>8WpYGrM0</t>
+          <t>6RCbX36s</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>fmqtFMjD</t>
+          <t>61T7bt5t</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>AeRSxQrK</t>
+          <t>GdWtpsjm</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>8j9FTL56</t>
+          <t>ERWFdKZh</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>U5cORazJ</t>
+          <t>8QPOfb45</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>dCkAk3SP</t>
+          <t>x6HuiG3U</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>lAUlrLKa</t>
+          <t>SUdkBJln</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>fNaktakC</t>
+          <t>lpob9cJb</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>2m3cvwKO</t>
+          <t>2Fanm72d</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>2g67Vsyf</t>
+          <t>INsZAAf3</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6RCbX36s</t>
+          <t>tvOWhxZH</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>61T7bt5t</t>
+          <t>U11vkTXq</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>GdWtpsjm</t>
+          <t>z1q67ylB</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>OMDVg8x9</t>
+          <t>rRQ6H30k</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>jXcAnQUr</t>
+          <t>dUjtW2Fr</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>fRe0c20b</t>
+          <t>MFnpCm7C</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>CnnJp4ae</t>
+          <t>UsklUtpe</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>bw1zAKS6</t>
+          <t>ddFjPf2b</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>GINCsvmn</t>
+          <t>Sh9BS8ig</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>x6klsVh3</t>
+          <t>dAfPwfHi</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>b3pRrrU7</t>
+          <t>pWQ6LC1N</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>WfkfPdXH</t>
+          <t>jiUEFsV1</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>SMr3Nz2U</t>
+          <t>dY0SOQjI</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>xYBLuIHb</t>
+          <t>hO8aNYWA</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>6os5wmhS</t>
+          <t>vDA9yPiL</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>Kl7vhn7L</t>
+          <t>hzeTFV7m</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>nw6fJO5K</t>
+          <t>Q9rcSKE7</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>bHPacsq1</t>
+          <t>zJCJQnM5</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>MwmHgKaN</t>
+          <t>QkntzCGG</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>lQl9etVA</t>
+          <t>Wn71woN8</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>KWD8eLDD</t>
+          <t>EkqxE9x0</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>xUXzYQFk</t>
+          <t>GEugARyP</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>CCV9JR0d</t>
+          <t>U32wGjPp</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>bsinRI25</t>
+          <t>hGzqjO6E</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>GbaVU03t</t>
+          <t>OrHrRGXo</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>tOTmlbNp</t>
+          <t>WQF2UUMt</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>nPQL4PjR</t>
+          <t>rkazN4LU</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>pWhdu9NF</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="1" t="inlineStr">
-        <is>
-          <t>6NnRD2Ts</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="1" t="inlineStr">
-        <is>
-          <t>2FcwTvYh</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="1" t="inlineStr">
-        <is>
-          <t>EBSD6oME</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="1" t="inlineStr">
-        <is>
-          <t>WSQqW4p2</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="1" t="inlineStr">
-        <is>
-          <t>vaX1LmWq</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="1" t="inlineStr">
-        <is>
-          <t>n1hhaOVo</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="1" t="inlineStr">
-        <is>
-          <t>vyoZBtbf</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="1" t="inlineStr">
-        <is>
-          <t>634r8bcJ</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="1" t="inlineStr">
-        <is>
-          <t>pbFTwdnB</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="1" t="inlineStr">
-        <is>
-          <t>697ha3El</t>
+          <t>hxlYyYo4</t>
         </is>
       </c>
     </row>

--- a/data/england/p6_deployment/data_preparation/clean_data/df_match_player_cleaned.xlsx
+++ b/data/england/p6_deployment/data_preparation/clean_data/df_match_player_cleaned.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:A46"/>
+  <dimension ref="A2:A21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="2">
@@ -568,181 +568,6 @@
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>rRQ6H30k</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="inlineStr">
-        <is>
-          <t>dUjtW2Fr</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="inlineStr">
-        <is>
-          <t>MFnpCm7C</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>UsklUtpe</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="1" t="inlineStr">
-        <is>
-          <t>ddFjPf2b</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="1" t="inlineStr">
-        <is>
-          <t>Sh9BS8ig</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="1" t="inlineStr">
-        <is>
-          <t>dAfPwfHi</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="1" t="inlineStr">
-        <is>
-          <t>pWQ6LC1N</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="1" t="inlineStr">
-        <is>
-          <t>jiUEFsV1</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="1" t="inlineStr">
-        <is>
-          <t>dY0SOQjI</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="1" t="inlineStr">
-        <is>
-          <t>hO8aNYWA</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="1" t="inlineStr">
-        <is>
-          <t>vDA9yPiL</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="1" t="inlineStr">
-        <is>
-          <t>hzeTFV7m</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="1" t="inlineStr">
-        <is>
-          <t>Q9rcSKE7</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="1" t="inlineStr">
-        <is>
-          <t>zJCJQnM5</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="1" t="inlineStr">
-        <is>
-          <t>QkntzCGG</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="1" t="inlineStr">
-        <is>
-          <t>Wn71woN8</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="1" t="inlineStr">
-        <is>
-          <t>EkqxE9x0</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="1" t="inlineStr">
-        <is>
-          <t>GEugARyP</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="1" t="inlineStr">
-        <is>
-          <t>U32wGjPp</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="1" t="inlineStr">
-        <is>
-          <t>hGzqjO6E</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="1" t="inlineStr">
-        <is>
-          <t>OrHrRGXo</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="1" t="inlineStr">
-        <is>
-          <t>WQF2UUMt</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="1" t="inlineStr">
-        <is>
-          <t>rkazN4LU</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="1" t="inlineStr">
-        <is>
-          <t>hxlYyYo4</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/england/p6_deployment/data_preparation/clean_data/df_match_player_cleaned.xlsx
+++ b/data/england/p6_deployment/data_preparation/clean_data/df_match_player_cleaned.xlsx
@@ -425,13 +425,195 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:A21"/>
+  <dimension ref="A1:S8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_1</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_1</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_2</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_2</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_3</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_3</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_1</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_1</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_2</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_2</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_3</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_3</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_4</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_4</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_5</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_5</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_6</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_6</t>
+        </is>
+      </c>
+    </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
           <t>8j9FTL56</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>MmgznMrP</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>igor</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>0rGKAqEi</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>march solomon</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>6PChQYLj</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>verbruggen bart</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>tKOLurpo</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>fish william</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>0lk9Mt7D</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>hojlund rasmus</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>OIp0Le1f</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>lindelof victor</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>OdyMQkkR</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>malacia tyrell</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>88iLXV0O</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>shaw luke</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>hSGFyXra</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>yoro leny</t>
         </is>
       </c>
     </row>
@@ -441,6 +623,32 @@
           <t>U5cORazJ</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>MLBAJ1cH</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>matheus franca</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -448,6 +656,56 @@
           <t>dCkAk3SP</t>
         </is>
       </c>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>8YT7Leas</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>coady conor</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>0MQtpIlG</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>daka patson</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>I126P2TJ</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>opoku nathaniel</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>4MHt8I1q</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>stolarczyk jakub</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -455,6 +713,80 @@
           <t>lAUlrLKa</t>
         </is>
       </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>GzxuaXeQ</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>bobb oscar</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>ljTPcIo2</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>broadhead nathan</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>M9Wf7hOh</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>burns wes</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>dQwpB3JT</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>clarke harrison</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>MwredEF5</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>donacien janoi</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>bXCwpSK5</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>hirst george</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>nX9CLJFA</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>philips kalvin</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -462,6 +794,40 @@
           <t>fNaktakC</t>
         </is>
       </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>EBDu7nbJ</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>bazunu gavin</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>rsMiiNaj</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>danilo</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -469,6 +835,80 @@
           <t>2m3cvwKO</t>
         </is>
       </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>nLRMnJtJ</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>bentancur rodrigo</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>QNEAuZc1</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>branthwaite jarrad</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>SI6IcTms</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>chermiti</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>zq8Uz4Ed</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>coleman seamus</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>zctP50uI</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>garner james</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>AFn0oV0O</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>patterson nathan</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>tdmI0fpF</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>young ashley</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -476,97 +916,56 @@
           <t>2g67Vsyf</t>
         </is>
       </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>6RCbX36s</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>61T7bt5t</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>GdWtpsjm</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>ERWFdKZh</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>8QPOfb45</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>x6HuiG3U</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>SUdkBJln</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>lpob9cJb</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>2Fanm72d</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>INsZAAf3</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>tvOWhxZH</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>U11vkTXq</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>z1q67ylB</t>
-        </is>
-      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>bcI1EvBk</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>kamara boubacar</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>x6Gedmgl</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>mings tyrone</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Qm0l3aod</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>tierney kieran</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>OSNvjZSP</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>tomiyasu takehiro</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/england/p6_deployment/data_preparation/clean_data/df_match_player_cleaned.xlsx
+++ b/data/england/p6_deployment/data_preparation/clean_data/df_match_player_cleaned.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S8"/>
+  <dimension ref="A1:U14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -519,124 +519,160 @@
           <t>player_name_miss_away_6</t>
         </is>
       </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_7</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_7</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>8j9FTL56</t>
+          <t>6RCbX36s</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>MmgznMrP</t>
+          <t>CWnkAe9t</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>igor</t>
+          <t>adams tyler</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0rGKAqEi</t>
+          <t>Yo9UV9Mc</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>march solomon</t>
+          <t>brooks david</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>6PChQYLj</t>
+          <t>C4hNaLoU</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>verbruggen bart</t>
+          <t>unal enes</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>tKOLurpo</t>
+          <t>nRvavHmI</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>fish william</t>
+          <t>botman sven</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>0lk9Mt7D</t>
+          <t>0fPiq0ST</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>hojlund rasmus</t>
+          <t>lascelles jamaal</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>OIp0Le1f</t>
+          <t>nR5TcNGS</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>lindelof victor</t>
+          <t>miley lewis</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>OdyMQkkR</t>
+          <t>0SebIVqC</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>malacia tyrell</t>
+          <t>schar fabian</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>88iLXV0O</t>
+          <t>fmQVO5TQ</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>shaw luke</t>
+          <t>tonali sandro</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>hSGFyXra</t>
+          <t>U7cO4mg3</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>yoro leny</t>
+          <t>white joe</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>YwKMvtoh</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>wilson callum</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>U5cORazJ</t>
+          <t>61T7bt5t</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>MLBAJ1cH</t>
+          <t>dU6MwnBl</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>matheus franca</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
+          <t>chiwome leon</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>jDBbY3US</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>david gonzalez</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>8Wq79aVu</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>kalajdzic sasa</t>
+        </is>
+      </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
@@ -649,11 +685,13 @@
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>dCkAk3SP</t>
+          <t>GdWtpsjm</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
@@ -664,160 +702,92 @@
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
-          <t>8YT7Leas</t>
+          <t>6qin1IFT</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>coady conor</t>
+          <t>da silva joshua</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>0MQtpIlG</t>
+          <t>tdO4c5vq</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>daka patson</t>
+          <t>henry rico</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>I126P2TJ</t>
+          <t>rcIXJMf9</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>opoku nathaniel</t>
+          <t>hickey aaron</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>4MHt8I1q</t>
+          <t>MmJb4MzQ</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>stolarczyk jakub</t>
+          <t>rodriguez thiago</t>
         </is>
       </c>
       <c r="P4" t="inlineStr"/>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>lAUlrLKa</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>GzxuaXeQ</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>bobb oscar</t>
-        </is>
-      </c>
+          <t>ERWFdKZh</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>ljTPcIo2</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>broadhead nathan</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>M9Wf7hOh</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>burns wes</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>dQwpB3JT</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>clarke harrison</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>MwredEF5</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>donacien janoi</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>bXCwpSK5</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>hirst george</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>nX9CLJFA</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>philips kalvin</t>
-        </is>
-      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>fNaktakC</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>EBDu7nbJ</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>bazunu gavin</t>
-        </is>
-      </c>
+          <t>8QPOfb45</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>rsMiiNaj</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>danilo</t>
-        </is>
-      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
@@ -828,136 +798,52 @@
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>2m3cvwKO</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>nLRMnJtJ</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>bentancur rodrigo</t>
-        </is>
-      </c>
+          <t>x6HuiG3U</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>QNEAuZc1</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>branthwaite jarrad</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>SI6IcTms</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>chermiti</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>zq8Uz4Ed</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>coleman seamus</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>zctP50uI</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>garner james</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>AFn0oV0O</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>patterson nathan</t>
-        </is>
-      </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>tdmI0fpF</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>young ashley</t>
-        </is>
-      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>2g67Vsyf</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>bcI1EvBk</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>kamara boubacar</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>x6Gedmgl</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>mings tyrone</t>
-        </is>
-      </c>
+          <t>SUdkBJln</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Qm0l3aod</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>tierney kieran</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>OSNvjZSP</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>tomiyasu takehiro</t>
-        </is>
-      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
@@ -966,6 +852,170 @@
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>lpob9cJb</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>2Fanm72d</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>INsZAAf3</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>tvOWhxZH</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>U11vkTXq</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>z1q67ylB</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/england/p6_deployment/data_preparation/clean_data/df_match_player_cleaned.xlsx
+++ b/data/england/p6_deployment/data_preparation/clean_data/df_match_player_cleaned.xlsx
@@ -425,15 +425,173 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:A11"/>
+  <dimension ref="A1:S19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_1</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_1</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_2</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_2</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_3</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_3</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_4</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_4</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_1</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_1</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_2</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_2</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_5</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_5</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_3</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_3</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_6</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_6</t>
+        </is>
+      </c>
+    </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
           <t>ERWFdKZh</t>
         </is>
       </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>viMb6g9n</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>gabriel jesus</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>QFt86bm1</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>merino mikel</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Qm0l3aod</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>tierney kieran</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>OSNvjZSP</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>tomiyasu takehiro</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>0rGKAqEi</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>march solomon</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>AZOU76Ou</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>o riley matthew</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -441,6 +599,80 @@
           <t>8QPOfb45</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>6qin1IFT</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>da silva joshua</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>tdO4c5vq</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>henry rico</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>rcIXJMf9</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>hickey aaron</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>MmJb4MzQ</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>rodriguez thiago</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>EBDu7nbJ</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>bazunu gavin</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>2L76lB8m</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>stewart ross</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>W6A3dA7c</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>toney ivan</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -448,6 +680,72 @@
           <t>x6HuiG3U</t>
         </is>
       </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>QNEAuZc1</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>branthwaite jarrad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>SI6IcTms</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>chermiti</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>AFn0oV0O</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>patterson nathan</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>CWnkAe9t</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>adams tyler</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Yo9UV9Mc</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>brooks david</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>C4hNaLoU</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>unal enes</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -455,6 +753,64 @@
           <t>SUdkBJln</t>
         </is>
       </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>ljTPcIo2</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>broadhead nathan</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>M9Wf7hOh</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>burns wes</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>dQwpB3JT</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>clarke harrison</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>MwredEF5</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>donacien janoi</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>bXCwpSK5</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>hirst george</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -462,6 +818,72 @@
           <t>lpob9cJb</t>
         </is>
       </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>0MQtpIlG</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>daka patson</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>I126P2TJ</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>opoku nathaniel</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>4MHt8I1q</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>stolarczyk jakub</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>hfxPh7Kn</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>cash matty</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>bcI1EvBk</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>kamara boubacar</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>x6Gedmgl</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>mings tyrone</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -469,6 +891,56 @@
           <t>2Fanm72d</t>
         </is>
       </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>rsMiiNaj</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>danilo</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>dU6MwnBl</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>chiwome leon</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>jDBbY3US</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>david gonzalez</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>8Wq79aVu</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>kalajdzic sasa</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -476,6 +948,40 @@
           <t>INsZAAf3</t>
         </is>
       </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>fcMqoMcH</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>cresswell aaron</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>GzxuaXeQ</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>bobb oscar</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
@@ -483,6 +989,40 @@
           <t>tvOWhxZH</t>
         </is>
       </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>MLBAJ1cH</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>matheus franca</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>dGshLigA</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>riad chadi</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -490,6 +1030,88 @@
           <t>U11vkTXq</t>
         </is>
       </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>nRvavHmI</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>botman sven</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>dp3dkdsI</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>dubravka martin</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>0fPiq0ST</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>lascelles jamaal</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>nR5TcNGS</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>miley lewis</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>nLRMnJtJ</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>bentancur rodrigo</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>OrADwZse</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>solanke dominic</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>0SebIVqC</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>schar fabian</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>YwKMvtoh</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>wilson callum</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
@@ -497,6 +1119,272 @@
           <t>z1q67ylB</t>
         </is>
       </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>0lk9Mt7D</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>hojlund rasmus</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>OIp0Le1f</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>lindelof victor</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>OdyMQkkR</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>malacia tyrell</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>lOA8VKIK</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>mount mason</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>88iLXV0O</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>shaw luke</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>hSGFyXra</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>yoro leny</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>2kGeEq1e</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>2TvL16Hk</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>beYTapn2</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>jkLFNmv9</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>AiyHLR8L</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>tzSnG5Wr</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>Wplk7SgS</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>AVat9lPF</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/england/p6_deployment/data_preparation/clean_data/df_match_player_cleaned.xlsx
+++ b/data/england/p6_deployment/data_preparation/clean_data/df_match_player_cleaned.xlsx
@@ -425,285 +425,76 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q4"/>
+  <dimension ref="A2:A11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1">
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_away_1</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_away_1</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_away_2</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_away_2</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_home_1</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_home_1</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_home_2</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_home_2</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_home_3</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_home_3</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_home_4</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_home_4</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_home_5</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_home_5</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_home_6</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_home_6</t>
-        </is>
-      </c>
-    </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>tvOWhxZH</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>MLBAJ1cH</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>matheus franca</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>dGshLigA</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>riad chadi</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
+          <t>2kGeEq1e</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>U11vkTXq</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>K82Dz773</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>richarlison</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>OrADwZse</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>solanke dominic</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>nRvavHmI</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>botman sven</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>dp3dkdsI</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>dubravka martin</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>0fPiq0ST</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>lascelles jamaal</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>nR5TcNGS</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>miley lewis</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0SebIVqC</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>schar fabian</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>YwKMvtoh</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>wilson callum</t>
+          <t>2TvL16Hk</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>z1q67ylB</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>0lk9Mt7D</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>hojlund rasmus</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>OIp0Le1f</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>lindelof victor</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>OdyMQkkR</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>malacia tyrell</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>lOA8VKIK</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>mount mason</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>88iLXV0O</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>shaw luke</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>hSGFyXra</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>yoro leny</t>
+          <t>beYTapn2</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>jkLFNmv9</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>AiyHLR8L</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>tzSnG5Wr</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>Wplk7SgS</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>AVat9lPF</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>AFJ3CNV7</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>Of1jzRNE</t>
         </is>
       </c>
     </row>

--- a/data/england/p6_deployment/data_preparation/clean_data/df_match_player_cleaned.xlsx
+++ b/data/england/p6_deployment/data_preparation/clean_data/df_match_player_cleaned.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:A11"/>
+  <dimension ref="A2:A21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="2">
@@ -498,6 +498,76 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>C0axT3Xo</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>d8abY4hR</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>pYXoP0FD</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>xtzXn47K</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>dQG3srVs</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>Q58Kw0U6</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>W2BSyvaJ</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>OIqwRMp1</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>GhtVSrGl</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>UwFBuMaf</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/england/p6_deployment/data_preparation/clean_data/df_match_player_cleaned.xlsx
+++ b/data/england/p6_deployment/data_preparation/clean_data/df_match_player_cleaned.xlsx
@@ -425,146 +425,238 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:A21"/>
+  <dimension ref="A1:Q3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_1</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_1</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_1</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_1</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_2</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_2</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_3</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_3</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_4</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_4</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_5</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_5</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_2</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_2</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_3</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_3</t>
+        </is>
+      </c>
+    </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>2kGeEq1e</t>
-        </is>
-      </c>
+          <t>AFJ3CNV7</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>K82Dz773</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>richarlison</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>QFt86bm1</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>merino mikel</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>ID32TGhp</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>odegaard martin</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>zkQ8Cm6n</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>rice declan</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Qm0l3aod</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>tierney kieran</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>OSNvjZSP</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>tomiyasu takehiro</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>2TvL16Hk</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>beYTapn2</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>jkLFNmv9</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>AiyHLR8L</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>tzSnG5Wr</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Wplk7SgS</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>AVat9lPF</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>AFJ3CNV7</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
           <t>Of1jzRNE</t>
         </is>
       </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>C0axT3Xo</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>d8abY4hR</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>pYXoP0FD</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>xtzXn47K</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>dQG3srVs</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>Q58Kw0U6</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>W2BSyvaJ</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>OIqwRMp1</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>GhtVSrGl</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>UwFBuMaf</t>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>dU6MwnBl</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>chiwome leon</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>nRvavHmI</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>botman sven</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0fPiq0ST</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>lascelles jamaal</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>nR5TcNGS</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>miley lewis</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>YwKMvtoh</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>wilson callum</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>jDBbY3US</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>david gonzalez</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>8Wq79aVu</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>kalajdzic sasa</t>
         </is>
       </c>
     </row>

--- a/data/england/p6_deployment/data_preparation/clean_data/df_match_player_cleaned.xlsx
+++ b/data/england/p6_deployment/data_preparation/clean_data/df_match_player_cleaned.xlsx
@@ -425,238 +425,146 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q3"/>
+  <dimension ref="A2:A21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1">
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_home_1</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_home_1</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_away_1</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_away_1</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_away_2</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_away_2</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_away_3</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_away_3</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_away_4</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_away_4</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_away_5</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_away_5</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_home_2</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_home_2</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_home_3</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_home_3</t>
-        </is>
-      </c>
-    </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>AFJ3CNV7</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>K82Dz773</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>richarlison</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>QFt86bm1</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>merino mikel</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>ID32TGhp</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>odegaard martin</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>zkQ8Cm6n</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>rice declan</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Qm0l3aod</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>tierney kieran</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>OSNvjZSP</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>tomiyasu takehiro</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
+          <t>C0axT3Xo</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Of1jzRNE</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>dU6MwnBl</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>chiwome leon</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>nRvavHmI</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>botman sven</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0fPiq0ST</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>lascelles jamaal</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>nR5TcNGS</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>miley lewis</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>YwKMvtoh</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>wilson callum</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>jDBbY3US</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>david gonzalez</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>8Wq79aVu</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>kalajdzic sasa</t>
+          <t>d8abY4hR</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>pYXoP0FD</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>xtzXn47K</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>dQG3srVs</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Q58Kw0U6</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>W2BSyvaJ</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>OIqwRMp1</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>GhtVSrGl</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>UwFBuMaf</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>8MkyzwoT</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>GhdgPLWA</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>l6f1Na1N</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>WQcQHwPp</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>bXkCusHi</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>4hy7UG8j</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>K0JghK0c</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>KnvLwLo4</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>SCsTyaGG</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>KQ2pRs2b</t>
         </is>
       </c>
     </row>

--- a/data/england/p6_deployment/data_preparation/clean_data/df_match_player_cleaned.xlsx
+++ b/data/england/p6_deployment/data_preparation/clean_data/df_match_player_cleaned.xlsx
@@ -425,15 +425,173 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:A21"/>
+  <dimension ref="A1:W11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_1</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_1</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_2</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_2</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_3</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_3</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_1</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_1</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_2</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_2</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_3</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_3</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_4</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_4</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_5</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_5</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_6</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_6</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_7</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_7</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_4</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_4</t>
+        </is>
+      </c>
+    </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
           <t>C0axT3Xo</t>
         </is>
       </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>YNCrLSO2</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>gusto malo</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>nLBC7ERa</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>james reece</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>84jK2uW3</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>kellyman omari</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -441,6 +599,84 @@
           <t>d8abY4hR</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>dU6MwnBl</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>chiwome leon</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>jDBbY3US</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>david gonzalez</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>8Wq79aVu</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>kalajdzic sasa</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>hfxPh7Kn</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>cash matty</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>bcI1EvBk</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>kamara boubacar</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>x6Gedmgl</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>mings tyrone</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>SESLDO0h</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>meupiyou menadjou bastien</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -448,6 +684,68 @@
           <t>pYXoP0FD</t>
         </is>
       </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>nRvavHmI</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>botman sven</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>0fPiq0ST</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>lascelles jamaal</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>nR5TcNGS</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>miley lewis</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>jwnLrX9d</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>carlos vinicius</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>YwKMvtoh</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>wilson callum</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -455,6 +753,84 @@
           <t>xtzXn47K</t>
         </is>
       </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>0rnu9an9</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>broja armando</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>SI6IcTms</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>chermiti</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>f12b2WQA</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>gueye idrissa</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0MQtpIlG</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>daka patson</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>I126P2TJ</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>opoku nathaniel</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>4MHt8I1q</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>stolarczyk jakub</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>AFn0oV0O</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>patterson nathan</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -462,6 +838,44 @@
           <t>dQG3srVs</t>
         </is>
       </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>CWnkAe9t</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>adams tyler</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>nBSzcorC</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>elliott harvey</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -469,6 +883,60 @@
           <t>Q58Kw0U6</t>
         </is>
       </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>MwredEF5</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>donacien janoi</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>EBDu7nbJ</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>bazunu gavin</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>lxFOy0k5</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>stephens jack</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>EksgGjXe</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>sulemana kamal deen</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -476,6 +944,100 @@
           <t>W2BSyvaJ</t>
         </is>
       </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>6qin1IFT</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>da silva joshua</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>r3Sue7SA</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>gustavo nunes</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>tdO4c5vq</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>henry rico</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>CIvgNZLk</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>odobert wilson</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>K82Dz773</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>richarlison</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>rcIXJMf9</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>hickey aaron</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Aijf2AQ6</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>jensen mathias</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>MmJb4MzQ</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>rodriguez thiago</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>b35gWzB2</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>wissa yoane</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
@@ -483,6 +1045,84 @@
           <t>OIqwRMp1</t>
         </is>
       </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>OIp0Le1f</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>lindelof victor</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>OdyMQkkR</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>malacia tyrell</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>88iLXV0O</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>shaw luke</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>M71HrXch</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>holding rob</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>MLBAJ1cH</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>matheus franca</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>dGshLigA</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>riad chadi</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>hSGFyXra</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>yoro leny</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -490,6 +1130,68 @@
           <t>GhtVSrGl</t>
         </is>
       </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>rsMiiNaj</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>danilo</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>4EjPxBOf</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>gruda brajan</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>0rGKAqEi</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>march solomon</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>QLY3kAEt</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>milner james</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>AZOU76Ou</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>o riley matthew</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
@@ -497,76 +1199,84 @@
           <t>UwFBuMaf</t>
         </is>
       </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>8MkyzwoT</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>GhdgPLWA</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>l6f1Na1N</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>WQcQHwPp</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>bXkCusHi</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>4hy7UG8j</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>K0JghK0c</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>KnvLwLo4</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>SCsTyaGG</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>KQ2pRs2b</t>
-        </is>
-      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>QFt86bm1</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>merino mikel</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>ID32TGhp</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>odegaard martin</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Qm0l3aod</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>tierney kieran</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>6LBvaQoh</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>ake nathan</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>GzxuaXeQ</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>bobb oscar</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>OSNvjZSP</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>tomiyasu takehiro</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>MwSCTKq6</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>zinchenko oleksandr</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/england/p6_deployment/data_preparation/clean_data/df_match_player_cleaned.xlsx
+++ b/data/england/p6_deployment/data_preparation/clean_data/df_match_player_cleaned.xlsx
@@ -425,238 +425,146 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q3"/>
+  <dimension ref="A2:A21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1">
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_home_1</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_home_1</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_away_1</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_away_1</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_away_2</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_away_2</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_away_3</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_away_3</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_away_4</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_away_4</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_away_5</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_away_5</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_home_2</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_home_2</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_home_3</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_home_3</t>
-        </is>
-      </c>
-    </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>AFJ3CNV7</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>K82Dz773</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>richarlison</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>QFt86bm1</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>merino mikel</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>ID32TGhp</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>odegaard martin</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>zkQ8Cm6n</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>rice declan</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Qm0l3aod</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>tierney kieran</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>OSNvjZSP</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>tomiyasu takehiro</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
+          <t>8MkyzwoT</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Of1jzRNE</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>dU6MwnBl</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>chiwome leon</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>nRvavHmI</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>botman sven</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0fPiq0ST</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>lascelles jamaal</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>nR5TcNGS</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>miley lewis</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>YwKMvtoh</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>wilson callum</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>jDBbY3US</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>david gonzalez</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>8Wq79aVu</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>kalajdzic sasa</t>
+          <t>GhdgPLWA</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>l6f1Na1N</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>WQcQHwPp</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>bXkCusHi</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>4hy7UG8j</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>K0JghK0c</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>KnvLwLo4</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>SCsTyaGG</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>KQ2pRs2b</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>r3Wq3yFF</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>SQM1jbV9</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>bFdtqGNq</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>YXAOeg7k</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>tbEWgXy2</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>d6dJHzU8</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>l0Zi1FqS</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>ltBAlx0M</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>nywy5cp3</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>fsjksfhd</t>
         </is>
       </c>
     </row>

--- a/data/england/p6_deployment/data_preparation/clean_data/df_match_player_cleaned.xlsx
+++ b/data/england/p6_deployment/data_preparation/clean_data/df_match_player_cleaned.xlsx
@@ -425,15 +425,205 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:A21"/>
+  <dimension ref="A1:W10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_1</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_1</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_2</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_2</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_3</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_3</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_4</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_4</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_1</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_1</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_2</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_2</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_3</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_3</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_5</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_5</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_6</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_6</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_4</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_4</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_7</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_7</t>
+        </is>
+      </c>
+    </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
           <t>8MkyzwoT</t>
         </is>
       </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>nRvavHmI</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>botman sven</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>0fPiq0ST</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>lascelles jamaal</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>nR5TcNGS</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>miley lewis</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>YwKMvtoh</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>wilson callum</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>6LBvaQoh</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>ake nathan</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>GzxuaXeQ</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>bobb oscar</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>K0G8DB00</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>rodri</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -441,6 +631,108 @@
           <t>GhdgPLWA</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>QFt86bm1</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>merino mikel</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>ID32TGhp</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>odegaard martin</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Qm0l3aod</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>tierney kieran</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>OSNvjZSP</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>tomiyasu takehiro</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>0MQtpIlG</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>daka patson</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>I126P2TJ</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>opoku nathaniel</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>4MHt8I1q</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>stolarczyk jakub</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>xUAbnjp2</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>trossard leandro</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>MwSCTKq6</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>zinchenko oleksandr</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>2mkPasKP</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>vestergaard jannik</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -448,6 +740,92 @@
           <t>l6f1Na1N</t>
         </is>
       </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>6qin1IFT</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>da silva joshua</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>r3Sue7SA</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>gustavo nunes</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>tdO4c5vq</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>henry rico</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>rcIXJMf9</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>hickey aaron</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>UkdzkdDr</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>alvarez edson</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Aijf2AQ6</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>jensen mathias</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>MmJb4MzQ</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>rodriguez thiago</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>b35gWzB2</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>wissa yoane</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -455,6 +833,68 @@
           <t>WQcQHwPp</t>
         </is>
       </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>nLBC7ERa</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>james reece</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>84jK2uW3</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>kellyman omari</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>0rGKAqEi</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>march solomon</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>QLY3kAEt</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>milner james</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>AZOU76Ou</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>o riley matthew</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -462,6 +902,76 @@
           <t>bXkCusHi</t>
         </is>
       </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>0rnu9an9</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>broja armando</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>SI6IcTms</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>chermiti</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>K6FMcLvN</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>doucoure cheick</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>M71HrXch</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>holding rob</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>MLBAJ1cH</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>matheus franca</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>dGshLigA</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>riad chadi</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -469,6 +979,60 @@
           <t>4hy7UG8j</t>
         </is>
       </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>rsMiiNaj</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>danilo</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>beZNT1bB</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>gibbs white morgan</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>0zOKXsla</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>sangare ibrahim</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>jwnLrX9d</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>carlos vinicius</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -476,6 +1040,84 @@
           <t>K0JghK0c</t>
         </is>
       </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>dU6MwnBl</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>chiwome leon</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>jDBbY3US</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>david gonzalez</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>8Wq79aVu</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>kalajdzic sasa</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>SESLDO0h</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>meupiyou menadjou bastien</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>nBSzcorC</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>elliott harvey</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>AeyqOcqS</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>mosquera yerson</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>I3feMxCH</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>traore boubacar</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
@@ -483,6 +1125,68 @@
           <t>KnvLwLo4</t>
         </is>
       </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>MwredEF5</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>donacien janoi</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>bcI1EvBk</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>kamara boubacar</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>rgGnzD2e</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>mcginn john</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>x6Gedmgl</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>mings tyrone</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>YV4xT3YE</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>philogene bidace jaden</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -490,83 +1194,76 @@
           <t>SCsTyaGG</t>
         </is>
       </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>KQ2pRs2b</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>r3Wq3yFF</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>SQM1jbV9</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>bFdtqGNq</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>YXAOeg7k</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>tbEWgXy2</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>d6dJHzU8</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>l0Zi1FqS</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>ltBAlx0M</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>nywy5cp3</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>fsjksfhd</t>
-        </is>
-      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>OIp0Le1f</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>lindelof victor</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>OdyMQkkR</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>malacia tyrell</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>88iLXV0O</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>shaw luke</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>hSGFyXra</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>yoro leny</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>CIvgNZLk</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>odobert wilson</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>K82Dz773</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>richarlison</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/england/p6_deployment/data_preparation/clean_data/df_match_player_cleaned.xlsx
+++ b/data/england/p6_deployment/data_preparation/clean_data/df_match_player_cleaned.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q4"/>
+  <dimension ref="A1:AA17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,255 +441,1180 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>id_player_miss_home_2</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_2</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_3</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_3</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_4</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_4</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_5</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_5</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
           <t>id_player_miss_away_1</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>player_name_miss_away_1</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>id_player_miss_away_2</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>player_name_miss_away_2</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_6</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_6</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_7</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_7</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>id_player_miss_away_3</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>player_name_miss_away_3</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>id_player_miss_away_4</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>player_name_miss_away_4</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_home_2</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_home_2</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_home_3</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_home_3</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_home_4</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_home_4</t>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_5</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_5</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_6</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_6</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>KnvLwLo4</t>
+          <t>r3Wq3yFF</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>MwredEF5</t>
+          <t>K6FMcLvN</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>donacien janoi</t>
+          <t>doucoure cheick</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>bcI1EvBk</t>
+          <t>M71HrXch</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>kamara boubacar</t>
+          <t>holding rob</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>rgGnzD2e</t>
+          <t>MLBAJ1cH</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>mcginn john</t>
+          <t>matheus franca</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>x6Gedmgl</t>
+          <t>dGshLigA</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>mings tyrone</t>
+          <t>riad chadi</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>YV4xT3YE</t>
+          <t>fVGFlDh2</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>philogene bidace jaden</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
+          <t>richards chris</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>nBSzcorC</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>elliott harvey</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
       <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>SCsTyaGG</t>
+          <t>SQM1jbV9</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>OIp0Le1f</t>
+          <t>ID32TGhp</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>lindelof victor</t>
+          <t>odegaard martin</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>CIvgNZLk</t>
+          <t>Qm0l3aod</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>odobert wilson</t>
+          <t>tierney kieran</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>K82Dz773</t>
+          <t>OSNvjZSP</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>richarlison</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
+          <t>tomiyasu takehiro</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>MwSCTKq6</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>zinchenko oleksandr</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>OdyMQkkR</t>
+          <t>EBDu7nbJ</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>malacia tyrell</t>
+          <t>bazunu gavin</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>88iLXV0O</t>
+          <t>EksgGjXe</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>shaw luke</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>hSGFyXra</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>yoro leny</t>
-        </is>
-      </c>
+          <t>sulemana kamal deen</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="inlineStr"/>
+      <c r="X3" t="inlineStr"/>
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="inlineStr"/>
+      <c r="AA3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>KQ2pRs2b</t>
+          <t>bFdtqGNq</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>6qin1IFT</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>da silva joshua</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>r3Sue7SA</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>gustavo nunes</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>tdO4c5vq</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>henry rico</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>rcIXJMf9</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>hickey aaron</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Aijf2AQ6</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>jensen mathias</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>dU6MwnBl</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>chiwome leon</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>jDBbY3US</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>david gonzalez</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>MmJb4MzQ</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>rodriguez thiago</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>b35gWzB2</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>wissa yoane</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>8Wq79aVu</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>kalajdzic sasa</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>SESLDO0h</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>meupiyou menadjou bastien</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>AeyqOcqS</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>mosquera yerson</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>I3feMxCH</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>traore boubacar</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>YXAOeg7k</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>roAKyGeS</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>choudhury hamza</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>0MQtpIlG</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>daka patson</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>I126P2TJ</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>opoku nathaniel</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>4MHt8I1q</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>stolarczyk jakub</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>2mkPasKP</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>vestergaard jannik</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
           <t>CWnkAe9t</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>adams tyler</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>EBDu7nbJ</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>bazunu gavin</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>EksgGjXe</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>sulemana kamal deen</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>tbEWgXy2</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>6LBvaQoh</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>ake nathan</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>GzxuaXeQ</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>bobb oscar</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>MsPs6OI5</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>de bruyne kevin</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>K0G8DB00</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>rodri</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>jwnLrX9d</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>carlos vinicius</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>I3b1w0I5</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>cuenca jorge</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr"/>
+      <c r="AA6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>d6dJHzU8</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>W2lXQVZs</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>cajuste jens lys</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr"/>
+      <c r="X7" t="inlineStr"/>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="inlineStr"/>
+      <c r="AA7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>l0Zi1FqS</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>0rnu9an9</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>broja armando</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>SI6IcTms</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>chermiti</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>zq8Uz4Ed</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>coleman seamus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>nRvavHmI</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>botman sven</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>p41IV42c</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>isak alexander</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>0fPiq0ST</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>lascelles jamaal</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>nR5TcNGS</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>miley lewis</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>YwKMvtoh</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>wilson callum</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr"/>
+      <c r="AA8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>ltBAlx0M</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>bcI1EvBk</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>kamara boubacar</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>rgGnzD2e</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>mcginn john</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>x6Gedmgl</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>mings tyrone</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>roId3gPf</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>onana amadou</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>URZH6b4K</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>ramsey jacob</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>OdyMQkkR</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>malacia tyrell</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>88iLXV0O</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>shaw luke</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>hSGFyXra</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>yoro leny</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr"/>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr"/>
+      <c r="AA9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>nywy5cp3</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>nLBC7ERa</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>james reece</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>84jK2uW3</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>kellyman omari</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>rsMiiNaj</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>danilo</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>0zOKXsla</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>sangare ibrahim</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="inlineStr"/>
+      <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr"/>
+      <c r="AA10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>fsjksfhd</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>0rGKAqEi</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>march solomon</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>QLY3kAEt</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>milner james</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>AZOU76Ou</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>o riley matthew</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>WG59HGIH</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>van hecke jan paul</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>CIvgNZLk</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>odobert wilson</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>K82Dz773</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>richarlison</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Mgg9oPeM</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>son heung min</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>ERi6Ggec</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>udogie iyenoma</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr"/>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr"/>
+      <c r="AA11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>OE9k61RO</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr"/>
+      <c r="X12" t="inlineStr"/>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr"/>
+      <c r="AA12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Y5lic6rf</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr"/>
+      <c r="W13" t="inlineStr"/>
+      <c r="X13" t="inlineStr"/>
+      <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="inlineStr"/>
+      <c r="AA13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>tWiaepD6</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr"/>
+      <c r="W14" t="inlineStr"/>
+      <c r="X14" t="inlineStr"/>
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="inlineStr"/>
+      <c r="AA14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>UiYgHRZP</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="inlineStr"/>
+      <c r="W15" t="inlineStr"/>
+      <c r="X15" t="inlineStr"/>
+      <c r="Y15" t="inlineStr"/>
+      <c r="Z15" t="inlineStr"/>
+      <c r="AA15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>n9EQB5cm</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr"/>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="inlineStr"/>
+      <c r="W16" t="inlineStr"/>
+      <c r="X16" t="inlineStr"/>
+      <c r="Y16" t="inlineStr"/>
+      <c r="Z16" t="inlineStr"/>
+      <c r="AA16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>Gl6s8NdC</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr"/>
+      <c r="T17" t="inlineStr"/>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="inlineStr"/>
+      <c r="W17" t="inlineStr"/>
+      <c r="X17" t="inlineStr"/>
+      <c r="Y17" t="inlineStr"/>
+      <c r="Z17" t="inlineStr"/>
+      <c r="AA17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/england/p6_deployment/data_preparation/clean_data/df_match_player_cleaned.xlsx
+++ b/data/england/p6_deployment/data_preparation/clean_data/df_match_player_cleaned.xlsx
@@ -425,452 +425,148 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O13"/>
+  <dimension ref="A2:A21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1">
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_home_1</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_home_1</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_away_1</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_away_1</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_away_2</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_away_2</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_away_3</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_away_3</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_home_2</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_home_2</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_home_3</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_home_3</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_home_4</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_home_4</t>
-        </is>
-      </c>
-    </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>ltBAlx0M</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>rgGnzD2e</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>mcginn john</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>GYvAMDm2</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>fernandes bruno</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>OdyMQkkR</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>malacia tyrell</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>hSGFyXra</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>yoro leny</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
+          <t>OE9k61RO</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>nywy5cp3</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>nLBC7ERa</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>james reece</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>rsMiiNaj</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>danilo</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0zOKXsla</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>sangare ibrahim</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>84jK2uW3</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>kellyman omari</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
+          <t>Y5lic6rf</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>fsjksfhd</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>CAmJERl2</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>joao pedro</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>CIvgNZLk</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>odobert wilson</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>K82Dz773</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>richarlison</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Mgg9oPeM</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>son heung min</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>0rGKAqEi</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>march solomon</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>AZOU76Ou</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>o riley matthew</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>WG59HGIH</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>van hecke jan paul</t>
+          <t>tWiaepD6</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>OE9k61RO</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
+          <t>UiYgHRZP</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Y5lic6rf</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
+          <t>n9EQB5cm</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>tWiaepD6</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
+          <t>Gl6s8NdC</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>UiYgHRZP</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
+          <t>ShJjaSDs</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>n9EQB5cm</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
+          <t>SSZaQ4Ct</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Gl6s8NdC</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
+          <t>2ot8gOsJ</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>ShJjaSDs</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
+          <t>KMCY9qSa</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>SSZaQ4Ct</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr"/>
+          <t>v5b6XwQN</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>2ot8gOsJ</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr"/>
+          <t>ABRGMMB5</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>rPPOK0tI</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>viJXIvBU</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>zypxSHmo</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>rw5cZaeB</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>EcDtwrdn</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>zD1kyMQb</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>EJlHkLuh</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>EqY7Orsg</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/england/p6_deployment/data_preparation/clean_data/df_match_player_cleaned.xlsx
+++ b/data/england/p6_deployment/data_preparation/clean_data/df_match_player_cleaned.xlsx
@@ -425,15 +425,185 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:A21"/>
+  <dimension ref="A1:Y21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_1</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_1</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_2</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_2</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_3</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_3</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_1</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_1</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_2</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_2</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_4</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_4</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_3</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_3</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_4</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_4</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_5</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_5</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_6</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_6</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_5</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_5</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_6</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_6</t>
+        </is>
+      </c>
+    </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
           <t>OE9k61RO</t>
         </is>
       </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>CIvgNZLk</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>odobert wilson</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>K82Dz773</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>richarlison</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Mgg9oPeM</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>son heung min</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -441,6 +611,54 @@
           <t>Y5lic6rf</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>jwnLrX9d</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>carlos vinicius</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>I3b1w0I5</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>cuenca jorge</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>rgGnzD2e</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>mcginn john</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="inlineStr"/>
+      <c r="X3" t="inlineStr"/>
+      <c r="Y3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -448,6 +666,62 @@
           <t>tWiaepD6</t>
         </is>
       </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>MwredEF5</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>donacien janoi</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>l21PrfBG</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>tuanzebe axel</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0rnu9an9</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>broja armando</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>SI6IcTms</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>chermiti</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr"/>
+      <c r="X4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -455,6 +729,110 @@
           <t>UiYgHRZP</t>
         </is>
       </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>xG8v3YRA</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>maguire harry</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>OdyMQkkR</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>malacia tyrell</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2ajowGAq</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>mazraoui noussair</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>6qin1IFT</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>da silva joshua</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>r3Sue7SA</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>gustavo nunes</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>hSGFyXra</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>yoro leny</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>tdO4c5vq</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>henry rico</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>rcIXJMf9</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>hickey aaron</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>MmJb4MzQ</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>rodriguez thiago</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>b35gWzB2</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>wissa yoane</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -462,6 +840,102 @@
           <t>n9EQB5cm</t>
         </is>
       </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>nRvavHmI</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>botman sven</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>p41IV42c</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>isak alexander</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>0fPiq0ST</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>lascelles jamaal</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>CAmJERl2</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>joao pedro</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>AZOU76Ou</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>o riley matthew</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>nR5TcNGS</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>miley lewis</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>WG59HGIH</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>van hecke jan paul</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>GMqWRFGS</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>trippier kieran</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>YwKMvtoh</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>wilson callum</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -469,6 +943,86 @@
           <t>Gl6s8NdC</t>
         </is>
       </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>EBDu7nbJ</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>bazunu gavin</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>KnkXb6uj</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>smallbone william</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>EksgGjXe</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>sulemana kamal deen</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>roAKyGeS</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>choudhury hamza</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>0MQtpIlG</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>daka patson</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>I126P2TJ</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>opoku nathaniel</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>4MHt8I1q</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>stolarczyk jakub</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr"/>
+      <c r="X7" t="inlineStr"/>
+      <c r="Y7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -476,6 +1030,62 @@
           <t>ShJjaSDs</t>
         </is>
       </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>ID32TGhp</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>odegaard martin</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>08NLEo06</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>saka bukayo</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Qm0l3aod</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>tierney kieran</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>MwSCTKq6</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>zinchenko oleksandr</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr"/>
+      <c r="X8" t="inlineStr"/>
+      <c r="Y8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
@@ -483,6 +1093,30 @@
           <t>SSZaQ4Ct</t>
         </is>
       </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr"/>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -490,6 +1124,30 @@
           <t>2ot8gOsJ</t>
         </is>
       </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="inlineStr"/>
+      <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
@@ -497,6 +1155,30 @@
           <t>KMCY9qSa</t>
         </is>
       </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr"/>
+      <c r="X11" t="inlineStr"/>
+      <c r="Y11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
@@ -504,6 +1186,30 @@
           <t>v5b6XwQN</t>
         </is>
       </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr"/>
+      <c r="X12" t="inlineStr"/>
+      <c r="Y12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
@@ -511,6 +1217,30 @@
           <t>ABRGMMB5</t>
         </is>
       </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr"/>
+      <c r="W13" t="inlineStr"/>
+      <c r="X13" t="inlineStr"/>
+      <c r="Y13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
@@ -518,6 +1248,30 @@
           <t>rPPOK0tI</t>
         </is>
       </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr"/>
+      <c r="W14" t="inlineStr"/>
+      <c r="X14" t="inlineStr"/>
+      <c r="Y14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
@@ -525,6 +1279,30 @@
           <t>viJXIvBU</t>
         </is>
       </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="inlineStr"/>
+      <c r="W15" t="inlineStr"/>
+      <c r="X15" t="inlineStr"/>
+      <c r="Y15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
@@ -532,6 +1310,30 @@
           <t>zypxSHmo</t>
         </is>
       </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr"/>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="inlineStr"/>
+      <c r="W16" t="inlineStr"/>
+      <c r="X16" t="inlineStr"/>
+      <c r="Y16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
@@ -539,6 +1341,30 @@
           <t>rw5cZaeB</t>
         </is>
       </c>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr"/>
+      <c r="T17" t="inlineStr"/>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="inlineStr"/>
+      <c r="W17" t="inlineStr"/>
+      <c r="X17" t="inlineStr"/>
+      <c r="Y17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
@@ -546,6 +1372,30 @@
           <t>EcDtwrdn</t>
         </is>
       </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr"/>
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="inlineStr"/>
+      <c r="W18" t="inlineStr"/>
+      <c r="X18" t="inlineStr"/>
+      <c r="Y18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
@@ -553,6 +1403,30 @@
           <t>zD1kyMQb</t>
         </is>
       </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="inlineStr"/>
+      <c r="T19" t="inlineStr"/>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="inlineStr"/>
+      <c r="W19" t="inlineStr"/>
+      <c r="X19" t="inlineStr"/>
+      <c r="Y19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
@@ -560,6 +1434,30 @@
           <t>EJlHkLuh</t>
         </is>
       </c>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr"/>
+      <c r="S20" t="inlineStr"/>
+      <c r="T20" t="inlineStr"/>
+      <c r="U20" t="inlineStr"/>
+      <c r="V20" t="inlineStr"/>
+      <c r="W20" t="inlineStr"/>
+      <c r="X20" t="inlineStr"/>
+      <c r="Y20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
@@ -567,6 +1465,30 @@
           <t>EqY7Orsg</t>
         </is>
       </c>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr"/>
+      <c r="S21" t="inlineStr"/>
+      <c r="T21" t="inlineStr"/>
+      <c r="U21" t="inlineStr"/>
+      <c r="V21" t="inlineStr"/>
+      <c r="W21" t="inlineStr"/>
+      <c r="X21" t="inlineStr"/>
+      <c r="Y21" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/england/p6_deployment/data_preparation/clean_data/df_match_player_cleaned.xlsx
+++ b/data/england/p6_deployment/data_preparation/clean_data/df_match_player_cleaned.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y21"/>
+  <dimension ref="A1:W21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -537,16 +537,6 @@
       <c r="W1" s="1" t="inlineStr">
         <is>
           <t>player_name_miss_home_5</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_home_6</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_home_6</t>
         </is>
       </c>
     </row>
@@ -602,8 +592,6 @@
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="inlineStr"/>
       <c r="W2" t="inlineStr"/>
-      <c r="X2" t="inlineStr"/>
-      <c r="Y2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -631,20 +619,36 @@
           <t>cuenca jorge</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>nwu2UvUA</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>lukic sasa</t>
+        </is>
+      </c>
       <c r="H3" t="inlineStr">
         <is>
+          <t>4CQLQWTa</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>konsa ezri</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>rgGnzD2e</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>mcginn john</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
@@ -657,8 +661,6 @@
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="inlineStr"/>
       <c r="W3" t="inlineStr"/>
-      <c r="X3" t="inlineStr"/>
-      <c r="Y3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -668,48 +670,64 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>bkbKtyxR</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>al hamadi ali</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
           <t>MwredEF5</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>donacien janoi</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Aw3OUCyR</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>luongo massimo</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0rnu9an9</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>broja armando</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>SI6IcTms</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>chermiti</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
         <is>
           <t>l21PrfBG</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>tuanzebe axel</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0rnu9an9</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>broja armando</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>SI6IcTms</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>chermiti</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
@@ -720,8 +738,6 @@
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="inlineStr"/>
       <c r="W4" t="inlineStr"/>
-      <c r="X4" t="inlineStr"/>
-      <c r="Y4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -831,8 +847,6 @@
       </c>
       <c r="V5" t="inlineStr"/>
       <c r="W5" t="inlineStr"/>
-      <c r="X5" t="inlineStr"/>
-      <c r="Y5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -852,22 +866,22 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>p41IV42c</t>
+          <t>0fPiq0ST</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>isak alexander</t>
+          <t>lascelles jamaal</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>0fPiq0ST</t>
+          <t>nR5TcNGS</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>lascelles jamaal</t>
+          <t>miley lewis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -882,60 +896,50 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
+          <t>0rGKAqEi</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>march solomon</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>GMqWRFGS</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>trippier kieran</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
           <t>AZOU76Ou</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>o riley matthew</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>nR5TcNGS</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>miley lewis</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>WG59HGIH</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>van hecke jan paul</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>IJd0tRWR</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>webster adam</t>
+        </is>
+      </c>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr"/>
       <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr"/>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>GMqWRFGS</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>trippier kieran</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>YwKMvtoh</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>wilson callum</t>
-        </is>
-      </c>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -965,12 +969,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>EksgGjXe</t>
+          <t>lxFOy0k5</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>sulemana kamal deen</t>
+          <t>stephens jack</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -993,8 +997,16 @@
           <t>daka patson</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>2L76lB8m</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>stewart ross</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr">
         <is>
           <t>I126P2TJ</t>
@@ -1021,8 +1033,6 @@
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="inlineStr"/>
       <c r="W7" t="inlineStr"/>
-      <c r="X7" t="inlineStr"/>
-      <c r="Y7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -1038,22 +1048,22 @@
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
+          <t>dbGArTGd</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>neto</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>ID32TGhp</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>odegaard martin</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>08NLEo06</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>saka bukayo</t>
         </is>
       </c>
       <c r="L8" t="inlineStr"/>
@@ -1084,8 +1094,6 @@
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="inlineStr"/>
       <c r="W8" t="inlineStr"/>
-      <c r="X8" t="inlineStr"/>
-      <c r="Y8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
@@ -1093,30 +1101,100 @@
           <t>SSZaQ4Ct</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr"/>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>dU6MwnBl</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>chiwome leon</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>jDBbY3US</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>david gonzalez</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>8Wq79aVu</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>kalajdzic sasa</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>6LBvaQoh</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>ake nathan</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>GzxuaXeQ</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>bobb oscar</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>AeyqOcqS</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>mosquera yerson</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>MsPs6OI5</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>de bruyne kevin</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>K0G8DB00</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>rodri</t>
+        </is>
+      </c>
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="inlineStr"/>
       <c r="T9" t="inlineStr"/>
       <c r="U9" t="inlineStr"/>
-      <c r="V9" t="inlineStr"/>
-      <c r="W9" t="inlineStr"/>
-      <c r="X9" t="inlineStr"/>
-      <c r="Y9" t="inlineStr"/>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>I3feMxCH</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>traore boubacar</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -1146,8 +1224,6 @@
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="inlineStr"/>
       <c r="W10" t="inlineStr"/>
-      <c r="X10" t="inlineStr"/>
-      <c r="Y10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
@@ -1177,8 +1253,6 @@
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="inlineStr"/>
       <c r="W11" t="inlineStr"/>
-      <c r="X11" t="inlineStr"/>
-      <c r="Y11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
@@ -1208,8 +1282,6 @@
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="inlineStr"/>
       <c r="W12" t="inlineStr"/>
-      <c r="X12" t="inlineStr"/>
-      <c r="Y12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
@@ -1239,8 +1311,6 @@
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="inlineStr"/>
       <c r="W13" t="inlineStr"/>
-      <c r="X13" t="inlineStr"/>
-      <c r="Y13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
@@ -1270,8 +1340,6 @@
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="inlineStr"/>
       <c r="W14" t="inlineStr"/>
-      <c r="X14" t="inlineStr"/>
-      <c r="Y14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
@@ -1301,8 +1369,6 @@
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="inlineStr"/>
       <c r="W15" t="inlineStr"/>
-      <c r="X15" t="inlineStr"/>
-      <c r="Y15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
@@ -1332,8 +1398,6 @@
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="inlineStr"/>
       <c r="W16" t="inlineStr"/>
-      <c r="X16" t="inlineStr"/>
-      <c r="Y16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
@@ -1363,8 +1427,6 @@
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="inlineStr"/>
       <c r="W17" t="inlineStr"/>
-      <c r="X17" t="inlineStr"/>
-      <c r="Y17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
@@ -1394,8 +1456,6 @@
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="inlineStr"/>
       <c r="W18" t="inlineStr"/>
-      <c r="X18" t="inlineStr"/>
-      <c r="Y18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
@@ -1425,8 +1485,6 @@
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="inlineStr"/>
       <c r="W19" t="inlineStr"/>
-      <c r="X19" t="inlineStr"/>
-      <c r="Y19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
@@ -1456,8 +1514,6 @@
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="inlineStr"/>
       <c r="W20" t="inlineStr"/>
-      <c r="X20" t="inlineStr"/>
-      <c r="Y20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
@@ -1487,8 +1543,6 @@
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="inlineStr"/>
       <c r="W21" t="inlineStr"/>
-      <c r="X21" t="inlineStr"/>
-      <c r="Y21" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/england/p6_deployment/data_preparation/clean_data/df_match_player_cleaned.xlsx
+++ b/data/england/p6_deployment/data_preparation/clean_data/df_match_player_cleaned.xlsx
@@ -425,15 +425,261 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:A21"/>
+  <dimension ref="A1:AE11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_1</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_1</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_2</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_2</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_3</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_3</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_4</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_4</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_5</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_5</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_1</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_1</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_2</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_2</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_3</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_3</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_6</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_6</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_7</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_7</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_4</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_4</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_5</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_5</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_6</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_6</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_7</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_7</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_8</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_8</t>
+        </is>
+      </c>
+    </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
           <t>v5b6XwQN</t>
         </is>
       </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>roAKyGeS</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>choudhury hamza</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>0MQtpIlG</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>daka patson</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>I126P2TJ</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>opoku nathaniel</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>4MHt8I1q</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>stolarczyk jakub</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>2mkPasKP</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>vestergaard jannik</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>rsMiiNaj</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>danilo</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0zOKXsla</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>sangare ibrahim</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>beZNT1bB</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>gibbs white morgan</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -441,6 +687,52 @@
           <t>ABRGMMB5</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>YV4xT3YE</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>philogene bidace jaden</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>CWnkAe9t</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>adams tyler</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="inlineStr"/>
+      <c r="X3" t="inlineStr"/>
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="inlineStr"/>
+      <c r="AA3" t="inlineStr"/>
+      <c r="AB3" t="inlineStr"/>
+      <c r="AC3" t="inlineStr"/>
+      <c r="AD3" t="inlineStr"/>
+      <c r="AE3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -448,6 +740,140 @@
           <t>rPPOK0tI</t>
         </is>
       </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>6qin1IFT</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>da silva joshua</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>r3Sue7SA</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>gustavo nunes</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>tdO4c5vq</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>henry rico</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>rcIXJMf9</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>hickey aaron</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>MmJb4MzQ</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>rodriguez thiago</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>MwredEF5</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>donacien janoi</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Aw3OUCyR</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>luongo massimo</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>l21PrfBG</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>tuanzebe axel</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>Aijf2AQ6</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>jensen mathias</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>b35gWzB2</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>wissa yoane</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>bkbKtyxR</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>al hamadi ali</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>W2lXQVZs</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>cajuste jens lys</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>4ETEZJ7p</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>o shea dara</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr"/>
+      <c r="AC4" t="inlineStr"/>
+      <c r="AD4" t="inlineStr"/>
+      <c r="AE4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -455,6 +881,148 @@
           <t>viJXIvBU</t>
         </is>
       </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>CAmJERl2</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>joao pedro</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>0rGKAqEi</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>march solomon</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>QLY3kAEt</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>milner james</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0Kp8MqA5</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>minteh yankuba</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>AZOU76Ou</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>o riley matthew</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>dU6MwnBl</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>chiwome leon</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>jDBbY3US</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>david gonzalez</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Sbw02Q2l</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>hwang hee chan</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>IJd0tRWR</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>webster adam</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Aod1noi7</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>johnstone sam</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>8Wq79aVu</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>kalajdzic sasa</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>AeyqOcqS</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>mosquera yerson</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>I3feMxCH</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>traore boubacar</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>SESLDO0h</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>meupiyou menadjou bastien</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -462,6 +1030,108 @@
           <t>zypxSHmo</t>
         </is>
       </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>GzxuaXeQ</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>bobb oscar</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>MsPs6OI5</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>de bruyne kevin</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>lMHcYK4f</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>doku jeremy</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>QVKaRfO9</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>grealish jack</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>K0G8DB00</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>rodri</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>EBDu7nbJ</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>bazunu gavin</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>IuutfkJB</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>fraser ryan</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>2L76lB8m</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>stewart ross</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>QeLg6KGD</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>walker kyle</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr"/>
+      <c r="AA6" t="inlineStr"/>
+      <c r="AB6" t="inlineStr"/>
+      <c r="AC6" t="inlineStr"/>
+      <c r="AD6" t="inlineStr"/>
+      <c r="AE6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -469,6 +1139,132 @@
           <t>rw5cZaeB</t>
         </is>
       </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>0rnu9an9</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>broja armando</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>SI6IcTms</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>chermiti</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>zctP50uI</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>garner james</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>zJaAPxhF</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>iroegbunam tim</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>AFn0oV0O</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>patterson nathan</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>AmMLTTJU</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>andersen joachim</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>jwnLrX9d</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>carlos vinicius</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>xYfOMcA5</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>castagne timothy</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>QNEAuZc1</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>branthwaite jarrad</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>d0pgiRk7</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>mykolenko vitali</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>I3b1w0I5</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>cuenca jorge</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>nwu2UvUA</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>lukic sasa</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr"/>
+      <c r="AA7" t="inlineStr"/>
+      <c r="AB7" t="inlineStr"/>
+      <c r="AC7" t="inlineStr"/>
+      <c r="AD7" t="inlineStr"/>
+      <c r="AE7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -476,6 +1272,92 @@
           <t>EcDtwrdn</t>
         </is>
       </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>84jK2uW3</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>kellyman omari</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>txvuTaNB</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>chilwell benjamin</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>nRvavHmI</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>botman sven</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>0fPiq0ST</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>lascelles jamaal</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>nR5TcNGS</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>miley lewis</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>GMqWRFGS</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>trippier kieran</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>YwKMvtoh</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>wilson callum</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr"/>
+      <c r="AA8" t="inlineStr"/>
+      <c r="AB8" t="inlineStr"/>
+      <c r="AC8" t="inlineStr"/>
+      <c r="AD8" t="inlineStr"/>
+      <c r="AE8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
@@ -483,6 +1365,92 @@
           <t>zD1kyMQb</t>
         </is>
       </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>M71HrXch</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>holding rob</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>MLBAJ1cH</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>matheus franca</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>dGshLigA</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>riad chadi</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>fVGFlDh2</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>richards chris</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>K6FMcLvN</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>doucoure cheick</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>Mgg9oPeM</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>son heung min</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>GQAxKWes</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>spence djed</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr"/>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr"/>
+      <c r="AA9" t="inlineStr"/>
+      <c r="AB9" t="inlineStr"/>
+      <c r="AC9" t="inlineStr"/>
+      <c r="AD9" t="inlineStr"/>
+      <c r="AE9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -490,6 +1458,108 @@
           <t>EJlHkLuh</t>
         </is>
       </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>zBydyE1a</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>fullkrug niclas</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>hzbcXxIG</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>kudus mohammed</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>xG8v3YRA</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>maguire harry</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>nBy3DbC3</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>mainoo kobbie</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>OdyMQkkR</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>malacia tyrell</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>lOA8VKIK</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>mount mason</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>88iLXV0O</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>shaw luke</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>hSGFyXra</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>yoro leny</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>Ukeq3c0b</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>casemiro</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr"/>
+      <c r="AE10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
@@ -497,76 +1567,132 @@
           <t>EqY7Orsg</t>
         </is>
       </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>WIs9mjGL</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>MqhPmaA4</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>lb85TUOk</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>rc1ER8g2</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>21YvrUwq</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>OGMmt88e</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>EJ4unbdE</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>drzevnw8</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>zil0kCo9</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>ratYowuH</t>
-        </is>
-      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>CEwq7x7l</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>calafiori riccardo</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>ID32TGhp</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>odegaard martin</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>EgIM3sB7</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>saliba william</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Qm0l3aod</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>tierney kieran</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>OSNvjZSP</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>tomiyasu takehiro</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>UZrQ3bwP</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>alisson</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>GM6fgd0p</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>bradley conor</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>jHMlMUC4</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>chiesa federico</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>08NLEo06</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>saka bukayo</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>hSaoLOM4</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>timber jurrien</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>nBSzcorC</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>elliott harvey</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>lr5I22zF</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>diogo jota</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr"/>
+      <c r="AA11" t="inlineStr"/>
+      <c r="AB11" t="inlineStr"/>
+      <c r="AC11" t="inlineStr"/>
+      <c r="AD11" t="inlineStr"/>
+      <c r="AE11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/england/p6_deployment/data_preparation/clean_data/df_match_player_cleaned.xlsx
+++ b/data/england/p6_deployment/data_preparation/clean_data/df_match_player_cleaned.xlsx
@@ -425,15 +425,333 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:A21"/>
+  <dimension ref="A1:AM11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_1</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_1</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_2</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_2</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_3</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_3</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_4</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_4</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_5</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_5</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_6</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_6</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_1</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_1</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_2</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_2</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_3</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_3</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_4</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_4</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_5</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_5</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_6</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_6</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_7</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_7</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_8</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_8</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_9</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_9</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_7</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_7</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_8</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_8</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_9</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_9</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_10</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_10</t>
+        </is>
+      </c>
+    </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
           <t>WIs9mjGL</t>
         </is>
       </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>nRvavHmI</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>botman sven</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>0fPiq0ST</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>lascelles jamaal</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>nR5TcNGS</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>miley lewis</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>GMqWRFGS</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>trippier kieran</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>YwKMvtoh</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>wilson callum</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>b5WYEjtm</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>murphy jacob</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>CEwq7x7l</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>calafiori riccardo</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>Qm0l3aod</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>tierney kieran</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>OSNvjZSP</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>tomiyasu takehiro</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>ID32TGhp</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>odegaard martin</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>pvGdJANj</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>white ben</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -441,6 +759,156 @@
           <t>MqhPmaA4</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>CWnkAe9t</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>adams tyler</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>boFdbMyt</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>scott alex</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Yq2dyUwN</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>arrizabalaga kepa</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0Q2tmFv8</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>billing philip</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>nqQejpdt</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>sinisterra luis</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>GzxuaXeQ</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>bobb oscar</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>MsPs6OI5</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>de bruyne kevin</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>lMHcYK4f</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>doku jeremy</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>QVKaRfO9</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>grealish jack</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>K0G8DB00</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>rodri</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>faynRsvT</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>savinho</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>QeLg6KGD</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>walker kyle</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>UJm2XpLH</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>akanji manuel</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>86K1f1fd</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>gvardiol josko</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="inlineStr"/>
+      <c r="AH3" t="inlineStr"/>
+      <c r="AI3" t="inlineStr"/>
+      <c r="AJ3" t="inlineStr"/>
+      <c r="AK3" t="inlineStr"/>
+      <c r="AL3" t="inlineStr"/>
+      <c r="AM3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -448,6 +916,172 @@
           <t>lb85TUOk</t>
         </is>
       </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>dQwpB3JT</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>clarke harrison</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>MwredEF5</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>donacien janoi</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>zJBUaWwh</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>greaves jacob</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Aw3OUCyR</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>luongo massimo</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>OOBNb1XC</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>ogbene chiedozie</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>tGd5gpeR</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>taylor jack</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0MQtpIlG</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>daka patson</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>I126P2TJ</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>opoku nathaniel</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>4MHt8I1q</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>stolarczyk jakub</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>roAKyGeS</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>choudhury hamza</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>bZdUUhdL</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>fataw issahaku</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>ILwRLjcF</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>kristiansen victor</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr"/>
+      <c r="AA4" t="inlineStr"/>
+      <c r="AB4" t="inlineStr"/>
+      <c r="AC4" t="inlineStr"/>
+      <c r="AD4" t="inlineStr"/>
+      <c r="AE4" t="inlineStr"/>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>l21PrfBG</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>tuanzebe axel</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>pQLd3K5k</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>giraud hutchinson omari</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>jRgdGLMG</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>johnson benjamin</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>4EwyHgmE</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>morsy sam</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -455,6 +1089,132 @@
           <t>rc1ER8g2</t>
         </is>
       </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>UZrQ3bwP</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>alisson</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>jHMlMUC4</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>chiesa federico</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>lr5I22zF</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>diogo jota</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>nBSzcorC</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>elliott harvey</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0rGKAqEi</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>march solomon</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>QLY3kAEt</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>milner james</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>IJd0tRWR</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>webster adam</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>xEyAI7pm</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>dunk lewis</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>CAmJERl2</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>joao pedro</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>0Kp8MqA5</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>minteh yankuba</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>AZOU76Ou</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>o riley matthew</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr"/>
+      <c r="AC5" t="inlineStr"/>
+      <c r="AD5" t="inlineStr"/>
+      <c r="AE5" t="inlineStr"/>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="inlineStr"/>
+      <c r="AH5" t="inlineStr"/>
+      <c r="AI5" t="inlineStr"/>
+      <c r="AJ5" t="inlineStr"/>
+      <c r="AK5" t="inlineStr"/>
+      <c r="AL5" t="inlineStr"/>
+      <c r="AM5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -462,6 +1222,100 @@
           <t>21YvrUwq</t>
         </is>
       </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>rsMiiNaj</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>danilo</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>0zOKXsla</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>sangare ibrahim</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>GxdkTszJ</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>ward prowse james</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>beZNT1bB</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>gibbs white morgan</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>MklkHcIh</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>jota ii</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>zBydyE1a</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>fullkrug niclas</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>hzbcXxIG</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>kudus mohammed</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr"/>
+      <c r="AA6" t="inlineStr"/>
+      <c r="AB6" t="inlineStr"/>
+      <c r="AC6" t="inlineStr"/>
+      <c r="AD6" t="inlineStr"/>
+      <c r="AE6" t="inlineStr"/>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="inlineStr"/>
+      <c r="AH6" t="inlineStr"/>
+      <c r="AI6" t="inlineStr"/>
+      <c r="AJ6" t="inlineStr"/>
+      <c r="AK6" t="inlineStr"/>
+      <c r="AL6" t="inlineStr"/>
+      <c r="AM6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -469,6 +1323,116 @@
           <t>OGMmt88e</t>
         </is>
       </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>EBDu7nbJ</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>bazunu gavin</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>KnkXb6uj</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>smallbone william</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2L76lB8m</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>stewart ross</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>6XOripaN</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>downes flynn</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>0rnu9an9</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>broja armando</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>SI6IcTms</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>chermiti</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>zctP50uI</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>garner james</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>zJaAPxhF</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>iroegbunam tim</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>2sHSjL7k</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>mcneil dwight</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr"/>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="inlineStr"/>
+      <c r="AA7" t="inlineStr"/>
+      <c r="AB7" t="inlineStr"/>
+      <c r="AC7" t="inlineStr"/>
+      <c r="AD7" t="inlineStr"/>
+      <c r="AE7" t="inlineStr"/>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="inlineStr"/>
+      <c r="AH7" t="inlineStr"/>
+      <c r="AI7" t="inlineStr"/>
+      <c r="AJ7" t="inlineStr"/>
+      <c r="AK7" t="inlineStr"/>
+      <c r="AL7" t="inlineStr"/>
+      <c r="AM7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -476,6 +1440,180 @@
           <t>EJ4unbdE</t>
         </is>
       </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>dU6MwnBl</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>chiwome leon</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>jDBbY3US</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>david gonzalez</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Sbw02Q2l</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>hwang hee chan</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>8Wq79aVu</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>kalajdzic sasa</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>AeyqOcqS</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>mosquera yerson</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>I3feMxCH</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>traore boubacar</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>M71HrXch</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>holding rob</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Es8aeBs4</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>lerma jefferson</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>MLBAJ1cH</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>matheus franca</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>dGshLigA</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>riad chadi</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>fVGFlDh2</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>richards chris</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>K6FMcLvN</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>doucoure cheick</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>Stf4BYFn</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>eze eberechi</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>v5IYUpDm</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>wharton adam</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr"/>
+      <c r="AE8" t="inlineStr"/>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>Aod1noi7</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>johnstone sam</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>dYDkA1lR</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>lemina mario</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>SESLDO0h</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>meupiyou menadjou bastien</t>
+        </is>
+      </c>
+      <c r="AL8" t="inlineStr"/>
+      <c r="AM8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
@@ -483,6 +1621,84 @@
           <t>drzevnw8</t>
         </is>
       </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>CIvgNZLk</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>odobert wilson</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>rotN6HH8</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>van de ven micky</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Mgg9oPeM</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>son heung min</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>GQAxKWes</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>spence djed</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>lbaPqFC9</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>werner timo</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr"/>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr"/>
+      <c r="AA9" t="inlineStr"/>
+      <c r="AB9" t="inlineStr"/>
+      <c r="AC9" t="inlineStr"/>
+      <c r="AD9" t="inlineStr"/>
+      <c r="AE9" t="inlineStr"/>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="inlineStr"/>
+      <c r="AH9" t="inlineStr"/>
+      <c r="AI9" t="inlineStr"/>
+      <c r="AJ9" t="inlineStr"/>
+      <c r="AK9" t="inlineStr"/>
+      <c r="AL9" t="inlineStr"/>
+      <c r="AM9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -490,6 +1706,124 @@
           <t>zil0kCo9</t>
         </is>
       </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>dIe4SZEK</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>antony</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>xG8v3YRA</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>maguire harry</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>nBy3DbC3</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>mainoo kobbie</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>88iLXV0O</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>shaw luke</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>hSGFyXra</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>yoro leny</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>nBRuYbqs</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>eriksen christian</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>84jK2uW3</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>kellyman omari</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>n5mG9yn6</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>sancho jadon</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="inlineStr"/>
+      <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr"/>
+      <c r="AA10" t="inlineStr"/>
+      <c r="AB10" t="inlineStr"/>
+      <c r="AC10" t="inlineStr"/>
+      <c r="AD10" t="inlineStr"/>
+      <c r="AE10" t="inlineStr"/>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>OdyMQkkR</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>malacia tyrell</t>
+        </is>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>lOA8VKIK</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>mount mason</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr"/>
+      <c r="AK10" t="inlineStr"/>
+      <c r="AL10" t="inlineStr"/>
+      <c r="AM10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
@@ -497,76 +1831,44 @@
           <t>ratYowuH</t>
         </is>
       </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>nX2mpxRQ</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>YTzyyYmD</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>K0RAmBXI</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>0d4cBEPP</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>6HqKvGll</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>0zTMbytK</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>KK9ggF3s</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>hY71igYg</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>CzO2kX26</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>CEnSxfJ0</t>
-        </is>
-      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr"/>
+      <c r="X11" t="inlineStr"/>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr"/>
+      <c r="AA11" t="inlineStr"/>
+      <c r="AB11" t="inlineStr"/>
+      <c r="AC11" t="inlineStr"/>
+      <c r="AD11" t="inlineStr"/>
+      <c r="AE11" t="inlineStr"/>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="inlineStr"/>
+      <c r="AH11" t="inlineStr"/>
+      <c r="AI11" t="inlineStr"/>
+      <c r="AJ11" t="inlineStr"/>
+      <c r="AK11" t="inlineStr"/>
+      <c r="AL11" t="inlineStr"/>
+      <c r="AM11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/england/p6_deployment/data_preparation/clean_data/df_match_player_cleaned.xlsx
+++ b/data/england/p6_deployment/data_preparation/clean_data/df_match_player_cleaned.xlsx
@@ -425,15 +425,269 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:A11"/>
+  <dimension ref="A1:AE18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_1</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_1</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_2</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_2</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_3</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_3</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_4</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_4</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_5</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_5</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_1</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_1</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_2</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_2</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_3</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_3</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_4</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_4</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_6</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_6</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_7</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_7</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_8</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_8</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_9</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_9</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_5</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_5</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_6</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_6</t>
+        </is>
+      </c>
+    </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
           <t>nX2mpxRQ</t>
         </is>
       </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>6qin1IFT</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>da silva joshua</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>r3Sue7SA</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>gustavo nunes</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>rcIXJMf9</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>hickey aaron</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>MmJb4MzQ</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>rodriguez thiago</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>tK0pMshb</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>ajer kristoffer</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>CWnkAe9t</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>adams tyler</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>GvqREHp3</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>ouattara dango</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>boFdbMyt</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>scott alex</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>nqQejpdt</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>sinisterra luis</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -441,6 +695,116 @@
           <t>YTzyyYmD</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Stf4BYFn</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>eze eberechi</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>M71HrXch</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>holding rob</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>j1OKB8dN</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>hughes will</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Es8aeBs4</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>lerma jefferson</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>MLBAJ1cH</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>matheus franca</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>nwu2UvUA</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>lukic sasa</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>dGshLigA</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>riad chadi</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>fVGFlDh2</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>richards chris</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>YF1DNCEB</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>ward joel</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>v5IYUpDm</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>wharton adam</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr"/>
+      <c r="AC3" t="inlineStr"/>
+      <c r="AD3" t="inlineStr"/>
+      <c r="AE3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -448,6 +812,108 @@
           <t>K0RAmBXI</t>
         </is>
       </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>UkdzkdDr</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>alvarez edson</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>zBydyE1a</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>fullkrug niclas</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>hzbcXxIG</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>kudus mohammed</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>0rnu9an9</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>broja armando</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>SI6IcTms</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>chermiti</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>zctP50uI</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>garner james</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>zJaAPxhF</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>iroegbunam tim</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr"/>
+      <c r="X4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr"/>
+      <c r="AA4" t="inlineStr"/>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>zq8Uz4Ed</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>coleman seamus</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>2sHSjL7k</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>mcneil dwight</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -455,6 +921,132 @@
           <t>0d4cBEPP</t>
         </is>
       </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>dU6MwnBl</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>chiwome leon</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>jDBbY3US</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>david gonzalez</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>8Wq79aVu</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>kalajdzic sasa</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>AeyqOcqS</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>mosquera yerson</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>I3feMxCH</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>traore boubacar</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>EBDu7nbJ</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>bazunu gavin</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>KnkXb6uj</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>smallbone william</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>2L76lB8m</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>stewart ross</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>IuutfkJB</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>fraser ryan</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Aod1noi7</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>johnstone sam</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>SESLDO0h</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>meupiyou menadjou bastien</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr"/>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>65ZQWgft</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>lallana adam</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr"/>
+      <c r="AE5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -462,6 +1054,140 @@
           <t>6HqKvGll</t>
         </is>
       </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>0rGKAqEi</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>march solomon</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>QLY3kAEt</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>milner james</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>IJd0tRWR</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>webster adam</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>vTrnQI0N</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>ayari yasin</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>xEyAI7pm</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>dunk lewis</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>GzxuaXeQ</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>bobb oscar</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>OpVD3nmU</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>dias ruben</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>QVKaRfO9</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>grealish jack</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>K0G8DB00</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>rodri</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>CAmJERl2</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>joao pedro</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>0Kp8MqA5</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>minteh yankuba</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>AZOU76Ou</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>o riley matthew</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr"/>
+      <c r="AA6" t="inlineStr"/>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>SlLxn4xl</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>stones john</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr"/>
+      <c r="AE6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -469,6 +1195,76 @@
           <t>0zTMbytK</t>
         </is>
       </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>UZrQ3bwP</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>alisson</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>jHMlMUC4</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>chiesa federico</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>lr5I22zF</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>diogo jota</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Stsozgbg</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>barkley ross</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>hfxPh7Kn</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>cash matty</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr"/>
+      <c r="X7" t="inlineStr"/>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="inlineStr"/>
+      <c r="AA7" t="inlineStr"/>
+      <c r="AB7" t="inlineStr"/>
+      <c r="AC7" t="inlineStr"/>
+      <c r="AD7" t="inlineStr"/>
+      <c r="AE7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -476,6 +1272,108 @@
           <t>KK9ggF3s</t>
         </is>
       </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>nBy3DbC3</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>mainoo kobbie</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>OdyMQkkR</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>malacia tyrell</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>88iLXV0O</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>shaw luke</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>hSGFyXra</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>yoro leny</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>I5Rhq1WL</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>traore amad</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>0MQtpIlG</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>daka patson</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>I126P2TJ</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>opoku nathaniel</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>4MHt8I1q</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>stolarczyk jakub</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>roAKyGeS</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>choudhury hamza</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr"/>
+      <c r="X8" t="inlineStr"/>
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="inlineStr"/>
+      <c r="AA8" t="inlineStr"/>
+      <c r="AB8" t="inlineStr"/>
+      <c r="AC8" t="inlineStr"/>
+      <c r="AD8" t="inlineStr"/>
+      <c r="AE8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
@@ -483,6 +1381,84 @@
           <t>hY71igYg</t>
         </is>
       </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>rsMiiNaj</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>danilo</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>0zOKXsla</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>sangare ibrahim</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>nRvavHmI</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>botman sven</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>0fPiq0ST</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>lascelles jamaal</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>nR5TcNGS</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>miley lewis</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>YwKMvtoh</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>wilson callum</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr"/>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr"/>
+      <c r="AA9" t="inlineStr"/>
+      <c r="AB9" t="inlineStr"/>
+      <c r="AC9" t="inlineStr"/>
+      <c r="AD9" t="inlineStr"/>
+      <c r="AE9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -490,6 +1466,132 @@
           <t>CzO2kX26</t>
         </is>
       </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>CIvgNZLk</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>odobert wilson</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>K82Dz773</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>richarlison</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>rotN6HH8</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>van de ven micky</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>zRAWGr3f</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>moore mikey</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>jBZTWXMn</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>romero cristian</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>MwredEF5</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>donacien janoi</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>zJBUaWwh</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>greaves jacob</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>OOBNb1XC</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>ogbene chiedozie</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>tGd5gpeR</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>taylor jack</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>GQAxKWes</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>spence djed</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>lbaPqFC9</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>werner timo</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr"/>
+      <c r="AA10" t="inlineStr"/>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>l21PrfBG</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>tuanzebe axel</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr"/>
+      <c r="AE10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
@@ -497,6 +1599,351 @@
           <t>CEnSxfJ0</t>
         </is>
       </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>84jK2uW3</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>kellyman omari</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>n5mG9yn6</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>sancho jadon</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>CEwq7x7l</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>calafiori riccardo</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>pfm9avwi</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>sterling raheem</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Qm0l3aod</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>tierney kieran</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>OSNvjZSP</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>tomiyasu takehiro</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr"/>
+      <c r="X11" t="inlineStr"/>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr"/>
+      <c r="AA11" t="inlineStr"/>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>zkQ8Cm6n</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>rice declan</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr"/>
+      <c r="AE11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>EubK3NNG</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr"/>
+      <c r="X12" t="inlineStr"/>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr"/>
+      <c r="AA12" t="inlineStr"/>
+      <c r="AB12" t="inlineStr"/>
+      <c r="AC12" t="inlineStr"/>
+      <c r="AD12" t="inlineStr"/>
+      <c r="AE12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Cl3y4WHa</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr"/>
+      <c r="W13" t="inlineStr"/>
+      <c r="X13" t="inlineStr"/>
+      <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="inlineStr"/>
+      <c r="AA13" t="inlineStr"/>
+      <c r="AB13" t="inlineStr"/>
+      <c r="AC13" t="inlineStr"/>
+      <c r="AD13" t="inlineStr"/>
+      <c r="AE13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>p21q2AnC</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr"/>
+      <c r="W14" t="inlineStr"/>
+      <c r="X14" t="inlineStr"/>
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="inlineStr"/>
+      <c r="AA14" t="inlineStr"/>
+      <c r="AB14" t="inlineStr"/>
+      <c r="AC14" t="inlineStr"/>
+      <c r="AD14" t="inlineStr"/>
+      <c r="AE14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>WveT5hmm</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="inlineStr"/>
+      <c r="W15" t="inlineStr"/>
+      <c r="X15" t="inlineStr"/>
+      <c r="Y15" t="inlineStr"/>
+      <c r="Z15" t="inlineStr"/>
+      <c r="AA15" t="inlineStr"/>
+      <c r="AB15" t="inlineStr"/>
+      <c r="AC15" t="inlineStr"/>
+      <c r="AD15" t="inlineStr"/>
+      <c r="AE15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>v3JHq2Wp</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr"/>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="inlineStr"/>
+      <c r="W16" t="inlineStr"/>
+      <c r="X16" t="inlineStr"/>
+      <c r="Y16" t="inlineStr"/>
+      <c r="Z16" t="inlineStr"/>
+      <c r="AA16" t="inlineStr"/>
+      <c r="AB16" t="inlineStr"/>
+      <c r="AC16" t="inlineStr"/>
+      <c r="AD16" t="inlineStr"/>
+      <c r="AE16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>69B375Oi</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr"/>
+      <c r="T17" t="inlineStr"/>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="inlineStr"/>
+      <c r="W17" t="inlineStr"/>
+      <c r="X17" t="inlineStr"/>
+      <c r="Y17" t="inlineStr"/>
+      <c r="Z17" t="inlineStr"/>
+      <c r="AA17" t="inlineStr"/>
+      <c r="AB17" t="inlineStr"/>
+      <c r="AC17" t="inlineStr"/>
+      <c r="AD17" t="inlineStr"/>
+      <c r="AE17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>A7iT11hT</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr"/>
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="inlineStr"/>
+      <c r="W18" t="inlineStr"/>
+      <c r="X18" t="inlineStr"/>
+      <c r="Y18" t="inlineStr"/>
+      <c r="Z18" t="inlineStr"/>
+      <c r="AA18" t="inlineStr"/>
+      <c r="AB18" t="inlineStr"/>
+      <c r="AC18" t="inlineStr"/>
+      <c r="AD18" t="inlineStr"/>
+      <c r="AE18" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
